--- a/03-product/calculadora/lista-precios-2026-07/lista-precios.xlsx
+++ b/03-product/calculadora/lista-precios-2026-07/lista-precios.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdmzi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AAAA96-01E4-4A60-A81E-F88FA3A59334}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8318AAB9-C350-4760-B202-A0B8CBFF8D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Copia de Para la Calculadora" sheetId="3" r:id="rId1"/>
+    <sheet name="usar este Diogenito" sheetId="4" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,12 +33,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="759">
   <si>
     <t>GUIDONI QUARTZ USD MARMOLES NATURALES</t>
   </si>
   <si>
-    <t>caculadora</t>
+    <t>precio calculadora</t>
   </si>
   <si>
     <t>Calacatta Gold</t>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Veta Silver (Negro) Apomazado Poro Abierto</t>
+  </si>
+  <si>
+    <t>Piedra Caliza Patagonica</t>
   </si>
   <si>
     <r>
@@ -383,7 +386,7 @@
     <t>NEGROS</t>
   </si>
   <si>
-    <t>Negro Brasil Estandar</t>
+    <t xml:space="preserve">Negro Brasil </t>
   </si>
   <si>
     <t>Negro Brasil Brushed</t>
@@ -392,10 +395,7 @@
     <t>Negro Zinbabwe Absoluto</t>
   </si>
   <si>
-    <t>Negro absoluto Dark (URUGUAYO)</t>
-  </si>
-  <si>
-    <t>Negro Semi Absoluto Dark</t>
+    <t xml:space="preserve">Negro absoluto Dark </t>
   </si>
   <si>
     <t>Eboni Cristal</t>
@@ -452,6 +452,9 @@
     <t>Blanco Fortaleza</t>
   </si>
   <si>
+    <t>Blanco Ceara</t>
+  </si>
+  <si>
     <t>GRANITOS GRIS- MARRON- ROSA-ROJO - MARMOLES NATURALES</t>
   </si>
   <si>
@@ -524,7 +527,7 @@
     <t>Bianco Gioia</t>
   </si>
   <si>
-    <t xml:space="preserve">Carrara Seleccion </t>
+    <t xml:space="preserve">Carrara </t>
   </si>
   <si>
     <t xml:space="preserve">Michelangelo </t>
@@ -776,15 +779,6 @@
     <t>Blanco Paloma (N y J)</t>
   </si>
   <si>
-    <t>Blanco Nube 1,2 cm (N)</t>
-  </si>
-  <si>
-    <t>Blanco Cana 24 1.2 cm (N)</t>
-  </si>
-  <si>
-    <t>Blanco Paloma 1,2 cm (N)</t>
-  </si>
-  <si>
     <t xml:space="preserve">GRUPO 1 </t>
   </si>
   <si>
@@ -887,159 +881,111 @@
     <t xml:space="preserve">Estatuario Venato </t>
   </si>
   <si>
-    <t>Serie smart+20mm (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arabescato Venatino </t>
-  </si>
-  <si>
-    <t>Calacatta Borghini</t>
+    <t>LISTA DE PRECIO - DEKTON +28% ES LA FORMULA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRUPO 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekton Domoos </t>
+  </si>
+  <si>
+    <t>Dekton kreto</t>
+  </si>
+  <si>
+    <t>Dekton Nebbia</t>
+  </si>
+  <si>
+    <t>GRUPO 1</t>
+  </si>
+  <si>
+    <t>Dekton Kelya</t>
+  </si>
+  <si>
+    <t>Dekton Zenith</t>
+  </si>
+  <si>
+    <t>Dekton Soke</t>
+  </si>
+  <si>
+    <t>Dekton Daze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekton Morpheus </t>
+  </si>
+  <si>
+    <t>Dekton Nara</t>
+  </si>
+  <si>
+    <t>GRUPO 2</t>
+  </si>
+  <si>
+    <t>Dekton Neural</t>
+  </si>
+  <si>
+    <t>Dekton Marmorio</t>
+  </si>
+  <si>
+    <t>Dekton Awoke</t>
+  </si>
+  <si>
+    <t>Dekton Lucid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekton Vigil </t>
+  </si>
+  <si>
+    <t>Dekton Somnia</t>
+  </si>
+  <si>
+    <t>Dekton khalo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dekton Halo </t>
+  </si>
+  <si>
+    <t>Dekton Danae</t>
+  </si>
+  <si>
+    <t>Dekton Sirius</t>
+  </si>
+  <si>
+    <t>Dekton Kairos</t>
+  </si>
+  <si>
+    <t>Dekton Marina</t>
+  </si>
+  <si>
+    <t>Dekton Sirocco</t>
+  </si>
+  <si>
+    <t>Dekton laurent</t>
   </si>
   <si>
     <t>GRUPO 4</t>
   </si>
   <si>
-    <t>Concrrete Sand (J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negro Betun </t>
-  </si>
-  <si>
-    <t>Pura Statuarietto 24 (J)</t>
-  </si>
-  <si>
-    <t>Pura  Statuario (J)</t>
-  </si>
-  <si>
-    <t>TAJ (J)</t>
-  </si>
-  <si>
-    <t>Calacatta D´or  (J)</t>
-  </si>
-  <si>
-    <t>Serie   Smart + 12mm( J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calacatta Clasico </t>
-  </si>
-  <si>
-    <t>Serie   Smart + 20mm( J)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calacatta Borghini </t>
-  </si>
-  <si>
-    <t>Calacatta  Clasico</t>
+    <t xml:space="preserve">Dekton Bromo </t>
+  </si>
+  <si>
+    <t>Dekton Keon</t>
+  </si>
+  <si>
+    <t>Dekton Salina</t>
+  </si>
+  <si>
+    <t>Dekton Nilium</t>
+  </si>
+  <si>
+    <t>Dekton Trilium</t>
+  </si>
+  <si>
+    <t>Dekton Radium</t>
   </si>
   <si>
     <t>GRUPO 5</t>
   </si>
   <si>
-    <t>Bianco Silver (J)*</t>
-  </si>
-  <si>
-    <t>Noir (J)*</t>
-  </si>
-  <si>
-    <t>LISTA DE PRECIO - DEKTON +28% ES LA FORMULA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GRUPO 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekton Domoos </t>
-  </si>
-  <si>
-    <t>Dekton kreto</t>
-  </si>
-  <si>
-    <t>Dekton Nebbia</t>
-  </si>
-  <si>
-    <t>GRUPO 1</t>
-  </si>
-  <si>
-    <t>Dekton Kelya</t>
-  </si>
-  <si>
-    <t>Dekton Zenith</t>
-  </si>
-  <si>
-    <t>Dekton Soke</t>
-  </si>
-  <si>
-    <t>Dekton Daze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekton Morpheus </t>
-  </si>
-  <si>
-    <t>Dekton Nara</t>
-  </si>
-  <si>
-    <t>GRUPO 2</t>
-  </si>
-  <si>
-    <t>Dekton Neural</t>
-  </si>
-  <si>
-    <t>Dekton Marmorio</t>
-  </si>
-  <si>
-    <t>Dekton Awoke</t>
-  </si>
-  <si>
-    <t>Dekton Lucid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekton Vigil </t>
-  </si>
-  <si>
-    <t>Dekton Somnia</t>
-  </si>
-  <si>
-    <t>Dekton khalo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekton Halo </t>
-  </si>
-  <si>
-    <t>Dekton Danae</t>
-  </si>
-  <si>
-    <t>Dekton Sirius</t>
-  </si>
-  <si>
-    <t>Dekton Kairos</t>
-  </si>
-  <si>
-    <t>Dekton Marina</t>
-  </si>
-  <si>
-    <t>Dekton Sirocco</t>
-  </si>
-  <si>
-    <t>Dekton laurent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dekton Bromo </t>
-  </si>
-  <si>
-    <t>Dekton Keon</t>
-  </si>
-  <si>
-    <t>Dekton Salina</t>
-  </si>
-  <si>
-    <t>Dekton Nilium</t>
-  </si>
-  <si>
-    <t>Dekton Trilium</t>
-  </si>
-  <si>
-    <t>Dekton Radium</t>
-  </si>
-  <si>
     <t>Dekton Aura</t>
   </si>
   <si>
@@ -1244,7 +1190,7 @@
     <t>Silestone Miami  Vena</t>
   </si>
   <si>
-    <t>Silestone White  Storm</t>
+    <t>Silestone White Storm</t>
   </si>
   <si>
     <t>Silestone Marengo</t>
@@ -1272,6 +1218,9 @@
   </si>
   <si>
     <t xml:space="preserve">Silestone Yukon </t>
+  </si>
+  <si>
+    <t>Silestone Blanco Zeus</t>
   </si>
   <si>
     <t xml:space="preserve">Silestone Calacatta Gold </t>
@@ -2464,7 +2413,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2481,6 +2430,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD5A6BD"/>
         <bgColor rgb="FFD5A6BD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -2508,7 +2463,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2519,22 +2474,31 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2758,15 +2722,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
+    <tabColor rgb="FFFF9900"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G918"/>
+  <dimension ref="A1:G881"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="53.42578125" customWidth="1"/>
+    <col min="1" max="1" width="56.42578125" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2783,7 +2748,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="2">
-        <v>1186.0419999999999</v>
+        <v>899.75600000000009</v>
       </c>
       <c r="C2" s="4"/>
       <c r="G2" s="5"/>
@@ -2793,7 +2758,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2">
-        <v>1186.0419999999999</v>
+        <v>899.75600000000009</v>
       </c>
       <c r="C3" s="4"/>
       <c r="G3" s="5"/>
@@ -2803,7 +2768,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="2">
-        <v>1186.0419999999999</v>
+        <v>899.75600000000009</v>
       </c>
       <c r="C4" s="4"/>
       <c r="G4" s="5"/>
@@ -2813,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="2">
-        <v>1022.45</v>
+        <v>736.1640000000001</v>
       </c>
       <c r="C5" s="4"/>
       <c r="G5" s="5"/>
@@ -2873,7 +2838,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="2">
-        <v>654.36800000000005</v>
+        <v>633.9190000000001</v>
       </c>
       <c r="C11" s="4"/>
       <c r="G11" s="5"/>
@@ -2893,7 +2858,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="2">
-        <v>858.85799999999995</v>
+        <v>736.1640000000001</v>
       </c>
       <c r="C13" s="4"/>
       <c r="G13" s="5"/>
@@ -2903,7 +2868,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="2">
-        <v>1022.45</v>
+        <v>736.1640000000001</v>
       </c>
       <c r="C14" s="4"/>
       <c r="G14" s="5"/>
@@ -2913,7 +2878,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="2">
-        <v>797.51100000000008</v>
+        <v>654.36800000000005</v>
       </c>
       <c r="C15" s="4"/>
       <c r="G15" s="5"/>
@@ -2923,7 +2888,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="2">
-        <v>1635.92</v>
+        <v>1226.94</v>
       </c>
       <c r="C16" s="4"/>
       <c r="G16" s="5"/>
@@ -2933,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="2">
-        <v>797.51100000000008</v>
+        <v>654.36800000000005</v>
       </c>
       <c r="C17" s="4"/>
       <c r="G17" s="5"/>
@@ -2943,7 +2908,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="2">
-        <v>879.30700000000002</v>
+        <v>715.71500000000015</v>
       </c>
       <c r="C18" s="4"/>
       <c r="G18" s="5"/>
@@ -2953,7 +2918,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="2">
-        <v>756.61300000000006</v>
+        <v>715.71500000000015</v>
       </c>
       <c r="C19" s="4"/>
       <c r="G19" s="5"/>
@@ -2963,7 +2928,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="2">
-        <v>1104.2460000000001</v>
+        <v>756.61300000000006</v>
       </c>
       <c r="C20" s="4"/>
       <c r="G20" s="5"/>
@@ -2973,7 +2938,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="2">
-        <v>817.96</v>
+        <v>756.61300000000006</v>
       </c>
       <c r="C21" s="4"/>
       <c r="G21" s="5"/>
@@ -2983,7 +2948,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="2">
-        <v>817.96</v>
+        <v>756.61300000000006</v>
       </c>
       <c r="C22" s="4"/>
       <c r="G22" s="5"/>
@@ -2993,7 +2958,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="2">
-        <v>1635.92</v>
+        <v>1226.94</v>
       </c>
       <c r="C23" s="4"/>
       <c r="G23" s="5"/>
@@ -3003,7 +2968,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="2">
-        <v>1226.94</v>
+        <v>899.75600000000009</v>
       </c>
       <c r="C24" s="4"/>
       <c r="G24" s="5"/>
@@ -3013,7 +2978,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="2">
-        <v>1022.45</v>
+        <v>756.61300000000006</v>
       </c>
       <c r="C25" s="4"/>
       <c r="G25" s="5"/>
@@ -3023,7 +2988,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="2">
-        <v>1124.6949999999999</v>
+        <v>756.61300000000006</v>
       </c>
       <c r="C26" s="4"/>
       <c r="G26" s="5"/>
@@ -3033,7 +2998,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="2">
-        <v>817.96</v>
+        <v>613.47</v>
       </c>
       <c r="C27" s="4"/>
       <c r="G27" s="5"/>
@@ -3049,18 +3014,18 @@
       <c r="G28" s="5"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="7" t="s">
         <v>28</v>
       </c>
       <c r="B29" s="2"/>
-      <c r="E29" s="7"/>
+      <c r="E29" s="8"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
       <c r="B30" s="2">
-        <v>715.71500000000015</v>
+        <v>633.9190000000001</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
@@ -3068,7 +3033,7 @@
         <v>30</v>
       </c>
       <c r="B31" s="2">
-        <v>715.71500000000015</v>
+        <v>633.9190000000001</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
@@ -3076,22 +3041,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="2">
-        <v>715.71500000000015</v>
+        <v>633.9190000000001</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B33" s="2"/>
-      <c r="E33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="E33" s="8"/>
+      <c r="G33" s="8"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="8"/>
-      <c r="E34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="E34" s="10"/>
       <c r="F34" s="4"/>
-      <c r="G34" s="10"/>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
@@ -3166,38 +3131,38 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="8"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="10"/>
+      <c r="B44" s="2">
+        <v>224939</v>
+      </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
+      <c r="A45" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="9"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" s="2">
         <v>1022.45</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="2"/>
-    </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="12" t="s">
-        <v>44</v>
-      </c>
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
+      <c r="A48" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="2">
-        <v>1840.41</v>
-      </c>
+      <c r="B48" s="2"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
@@ -3216,18 +3181,18 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B51" s="2"/>
+      <c r="B51" s="2">
+        <v>1840.41</v>
+      </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
+      <c r="A52" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="B52" s="2">
-        <v>1840.41</v>
-      </c>
+      <c r="B52" s="2"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="3" t="s">
@@ -3238,38 +3203,38 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="B54" s="2">
         <v>1840.41</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="10"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B55" s="8"/>
-      <c r="E55" s="9"/>
+      <c r="B55" s="2">
+        <v>1840.41</v>
+      </c>
+      <c r="E55" s="10"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="10"/>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B56" s="8"/>
-      <c r="E56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="E56" s="10"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="10"/>
+      <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+      <c r="A57" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B57" s="2">
-        <v>2453.88</v>
-      </c>
+      <c r="B57" s="9"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="4"/>
+      <c r="G57" s="11"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="3" t="s">
@@ -3312,37 +3277,37 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B63" s="2"/>
+      <c r="A63" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2">
+        <v>2453.88</v>
+      </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B64" s="2"/>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="1" t="s">
-        <v>59</v>
-      </c>
       <c r="B65" s="2"/>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="12" t="s">
+      <c r="A66" s="1" t="s">
         <v>60</v>
       </c>
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="3" t="s">
+      <c r="A67" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B67" s="2">
-        <v>552.12300000000005</v>
-      </c>
+      <c r="B67" s="2"/>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
         <v>62</v>
       </c>
       <c r="B68" s="2">
-        <v>408.98</v>
+        <v>552.12300000000005</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
@@ -3350,7 +3315,7 @@
         <v>63</v>
       </c>
       <c r="B69" s="2">
-        <v>695.26599999999996</v>
+        <v>408.98</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
@@ -3358,7 +3323,7 @@
         <v>64</v>
       </c>
       <c r="B70" s="2">
-        <v>572.57200000000012</v>
+        <v>695.26599999999996</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
@@ -3366,7 +3331,7 @@
         <v>65</v>
       </c>
       <c r="B71" s="2">
-        <v>695.26599999999996</v>
+        <v>572.57200000000012</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
@@ -3374,7 +3339,7 @@
         <v>66</v>
       </c>
       <c r="B72" s="2">
-        <v>777.06200000000001</v>
+        <v>695.26599999999996</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
@@ -3382,7 +3347,7 @@
         <v>67</v>
       </c>
       <c r="B73" s="2">
-        <v>654.36800000000005</v>
+        <v>777.06200000000001</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
@@ -3390,25 +3355,25 @@
         <v>68</v>
       </c>
       <c r="B74" s="2">
+        <v>654.36800000000005</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B75" s="2">
         <v>511.22500000000002</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B75" s="2"/>
-    </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="B76" s="2"/>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="3" t="s">
+      <c r="A77" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B77" s="2">
-        <v>470.32700000000006</v>
-      </c>
+      <c r="B77" s="2"/>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
@@ -3431,7 +3396,7 @@
         <v>73</v>
       </c>
       <c r="B80" s="2">
-        <v>286.28600000000006</v>
+        <v>470.32700000000006</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
@@ -3443,25 +3408,25 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B82" s="2"/>
+      <c r="B82" s="2">
+        <v>286.28600000000006</v>
+      </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="3" t="s">
+      <c r="A83" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B83" s="2">
-        <v>282.19619999999998</v>
-      </c>
+      <c r="B83" s="2"/>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
         <v>77</v>
       </c>
       <c r="B84" s="2">
-        <v>245.38800000000001</v>
+        <v>282.19619999999998</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
@@ -3469,7 +3434,7 @@
         <v>78</v>
       </c>
       <c r="B85" s="2">
-        <v>229.02880000000002</v>
+        <v>245.38800000000001</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
@@ -3477,7 +3442,7 @@
         <v>79</v>
       </c>
       <c r="B86" s="2">
-        <v>368.08200000000005</v>
+        <v>229.02880000000002</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
@@ -3485,7 +3450,7 @@
         <v>80</v>
       </c>
       <c r="B87" s="2">
-        <v>286.28600000000006</v>
+        <v>368.08200000000005</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
@@ -3493,7 +3458,7 @@
         <v>81</v>
       </c>
       <c r="B88" s="2">
-        <v>245.38800000000001</v>
+        <v>286.28600000000006</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
@@ -3501,7 +3466,7 @@
         <v>82</v>
       </c>
       <c r="B89" s="2">
-        <v>265.83700000000005</v>
+        <v>245.38800000000001</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
@@ -3509,7 +3474,7 @@
         <v>83</v>
       </c>
       <c r="B90" s="2">
-        <v>306.73500000000001</v>
+        <v>265.83700000000005</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
@@ -3517,7 +3482,7 @@
         <v>84</v>
       </c>
       <c r="B91" s="2">
-        <v>368.08200000000005</v>
+        <v>306.73500000000001</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
@@ -3541,7 +3506,7 @@
         <v>87</v>
       </c>
       <c r="B94" s="2">
-        <v>347.63299999999998</v>
+        <v>368.08200000000005</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
@@ -3549,7 +3514,7 @@
         <v>88</v>
       </c>
       <c r="B95" s="2">
-        <v>368.08200000000005</v>
+        <v>347.63299999999998</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
@@ -3557,7 +3522,7 @@
         <v>89</v>
       </c>
       <c r="B96" s="2">
-        <v>490.77600000000001</v>
+        <v>368.08200000000005</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
@@ -3565,7 +3530,7 @@
         <v>90</v>
       </c>
       <c r="B97" s="2">
-        <v>388.53100000000001</v>
+        <v>490.77600000000001</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
@@ -3573,53 +3538,53 @@
         <v>91</v>
       </c>
       <c r="B98" s="2">
+        <v>388.53100000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B99" s="2">
         <v>572.57200000000012</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B99" s="2"/>
-    </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="14" t="s">
+      <c r="A100" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B100" s="2"/>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="14" t="s">
+      <c r="A101" s="16" t="s">
         <v>94</v>
       </c>
       <c r="B101" s="2"/>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="16" t="s">
         <v>95</v>
       </c>
       <c r="B102" s="2"/>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="12" t="s">
+      <c r="A103" s="1" t="s">
         <v>96</v>
       </c>
       <c r="B103" s="2"/>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="3" t="s">
+      <c r="A104" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="B104" s="2">
-        <v>368.08200000000005</v>
-      </c>
+      <c r="B104" s="2"/>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
         <v>98</v>
       </c>
       <c r="B105" s="2">
-        <v>490.77600000000001</v>
+        <v>353.92500000000001</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
@@ -3627,7 +3592,7 @@
         <v>99</v>
       </c>
       <c r="B106" s="2">
-        <v>1186.0419999999999</v>
+        <v>471.90000000000003</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
@@ -3635,7 +3600,7 @@
         <v>100</v>
       </c>
       <c r="B107" s="2">
-        <v>715.71500000000015</v>
+        <v>1140.425</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
@@ -3643,7 +3608,7 @@
         <v>101</v>
       </c>
       <c r="B108" s="2">
-        <v>531.67400000000009</v>
+        <v>688.1875</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
@@ -3651,7 +3616,7 @@
         <v>102</v>
       </c>
       <c r="B109" s="2">
-        <v>449.87800000000004</v>
+        <v>432.57499999999999</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
@@ -3659,7 +3624,7 @@
         <v>103</v>
       </c>
       <c r="B110" s="2">
-        <v>490.77600000000001</v>
+        <v>471.90000000000003</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
@@ -3667,7 +3632,7 @@
         <v>104</v>
       </c>
       <c r="B111" s="2">
-        <v>1165.5930000000003</v>
+        <v>1120.7625</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
@@ -3748,7 +3713,7 @@
         <v>113</v>
       </c>
       <c r="B124" s="2">
-        <v>347.63299999999998</v>
+        <v>511.22500000000002</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
@@ -3756,7 +3721,7 @@
         <v>114</v>
       </c>
       <c r="B125" s="2">
-        <v>347.63299999999998</v>
+        <v>511.22500000000002</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
@@ -3764,7 +3729,7 @@
         <v>115</v>
       </c>
       <c r="B126" s="2">
-        <v>327.18400000000003</v>
+        <v>408.98</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
@@ -3783,7 +3748,7 @@
         <v>817.96</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
         <v>118</v>
       </c>
@@ -3791,7 +3756,7 @@
         <v>1574.5730000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
         <v>119</v>
       </c>
@@ -3799,90 +3764,95 @@
         <v>408.98</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="3"/>
-      <c r="B131" s="2"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B131" s="2">
+        <v>593.125</v>
+      </c>
+      <c r="C131" s="6"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="2"/>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B133" s="2"/>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A134" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B134" s="2"/>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B135" s="2">
         <v>368.08200000000005</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B136" s="2">
         <v>224.93900000000002</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B137" s="2"/>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A138" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B138" s="2"/>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B139" s="2">
         <v>261747.20000000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B140" s="2">
         <v>261747.20000000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B141" s="2">
         <v>339453.4</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B142" s="2">
         <v>339453.4</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B143" s="2">
         <v>259702.30000000002</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B144" s="2">
         <v>323094.2</v>
@@ -3890,7 +3860,7 @@
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B145" s="2">
         <v>370126.9</v>
@@ -3898,7 +3868,7 @@
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B146" s="2">
         <v>408980</v>
@@ -3906,7 +3876,7 @@
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B147" s="2">
         <v>408980</v>
@@ -3914,7 +3884,7 @@
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B148" s="2">
         <v>339453.4</v>
@@ -3922,7 +3892,7 @@
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B149" s="2">
         <v>339453.4</v>
@@ -3930,7 +3900,7 @@
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B150" s="2">
         <v>339453.4</v>
@@ -3938,7 +3908,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B151" s="2">
         <v>339453.4</v>
@@ -3946,7 +3916,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B152" s="2">
         <v>339453.4</v>
@@ -3954,7 +3924,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B153" s="2">
         <v>339453.4</v>
@@ -3964,14 +3934,14 @@
       <c r="B154" s="2"/>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="1" t="s">
-        <v>139</v>
+      <c r="A155" s="17" t="s">
+        <v>140</v>
       </c>
       <c r="B155" s="2"/>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B156" s="2">
         <v>347633</v>
@@ -3979,7 +3949,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B157" s="2">
         <v>347633</v>
@@ -3989,18 +3959,18 @@
       <c r="B158" s="2"/>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="14"/>
+      <c r="A159" s="16"/>
       <c r="B159" s="2"/>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B160" s="2"/>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B161" s="2">
         <v>1002.001</v>
@@ -4008,7 +3978,7 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B162" s="2">
         <v>981.55200000000002</v>
@@ -4016,7 +3986,7 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B163" s="2">
         <v>817.96</v>
@@ -4024,7 +3994,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B164" s="2">
         <v>3476.33</v>
@@ -4032,7 +4002,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B165" s="2">
         <v>1226.94</v>
@@ -4040,7 +4010,7 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B166" s="2">
         <v>4048.9020000000005</v>
@@ -4048,7 +4018,7 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B167" s="2">
         <v>899.75600000000009</v>
@@ -4056,7 +4026,7 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B168" s="2">
         <v>1022.45</v>
@@ -4064,7 +4034,7 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B169" s="2">
         <v>552.12300000000005</v>
@@ -4072,7 +4042,7 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B170" s="2">
         <v>408.98</v>
@@ -4080,7 +4050,7 @@
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B171" s="2">
         <v>1431.4300000000003</v>
@@ -4088,7 +4058,7 @@
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B172" s="2">
         <v>1533.675</v>
@@ -4096,7 +4066,7 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B173" s="2">
         <v>1533.675</v>
@@ -4104,7 +4074,7 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B174" s="2">
         <v>736.1640000000001</v>
@@ -4112,7 +4082,7 @@
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B175" s="2">
         <v>817.96</v>
@@ -4120,7 +4090,7 @@
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B176" s="2">
         <v>1431.4300000000003</v>
@@ -4132,13 +4102,13 @@
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B178" s="2"/>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B179" s="2">
         <v>1226.94</v>
@@ -4146,7 +4116,7 @@
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B180" s="2">
         <v>572.57200000000012</v>
@@ -4154,7 +4124,7 @@
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B181" s="2">
         <v>1124.6949999999999</v>
@@ -4162,7 +4132,7 @@
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B182" s="2">
         <v>817.96</v>
@@ -4170,7 +4140,7 @@
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B183" s="2">
         <v>3885.3100000000004</v>
@@ -4178,7 +4148,7 @@
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B184" s="2">
         <v>4907.76</v>
@@ -4186,13 +4156,13 @@
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B185" s="2"/>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B186" s="2">
         <v>817.96</v>
@@ -4200,7 +4170,7 @@
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B187" s="2">
         <v>1002.001</v>
@@ -4208,7 +4178,7 @@
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B188" s="2">
         <v>695.26599999999996</v>
@@ -4216,7 +4186,7 @@
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B189" s="2">
         <v>1002.001</v>
@@ -4224,7 +4194,7 @@
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B190" s="2">
         <v>736.1640000000001</v>
@@ -4232,7 +4202,7 @@
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B191" s="2">
         <v>1533.675</v>
@@ -4240,7 +4210,7 @@
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B192" s="2">
         <v>408.98</v>
@@ -4248,7 +4218,7 @@
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B193" s="2">
         <v>1922.2060000000001</v>
@@ -4256,21 +4226,21 @@
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B194" s="2"/>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="12" t="s">
-        <v>176</v>
+      <c r="A195" s="13" t="s">
+        <v>177</v>
       </c>
       <c r="B195" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="7" t="s">
-        <v>177</v>
+      <c r="A196" s="8" t="s">
+        <v>178</v>
       </c>
       <c r="B196" s="2">
         <v>660.66000000000008</v>
@@ -4278,7 +4248,7 @@
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B197" s="2">
         <v>660.66000000000008</v>
@@ -4286,7 +4256,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B198" s="2">
         <v>660.66000000000008</v>
@@ -4294,7 +4264,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B199" s="2">
         <v>660.66000000000008</v>
@@ -4302,23 +4272,23 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B200" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B201" s="2">
+      <c r="A201" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B201" s="15">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A202" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B202" s="2">
         <v>660.66000000000008</v>
@@ -4326,23 +4296,23 @@
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A203" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B203" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B204" s="2">
+      <c r="A204" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B204" s="15">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A205" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B205" s="2">
         <v>660.66000000000008</v>
@@ -4350,7 +4320,7 @@
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B206" s="2">
         <v>660.66000000000008</v>
@@ -4358,7 +4328,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A207" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B207" s="2">
         <v>660.66000000000008</v>
@@ -4366,7 +4336,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B208" s="2">
         <v>660.66000000000008</v>
@@ -4374,7 +4344,7 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B209" s="2">
         <v>660.66000000000008</v>
@@ -4382,7 +4352,7 @@
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B210" s="2">
         <v>660.66000000000008</v>
@@ -4390,7 +4360,7 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B211" s="2">
         <v>660.66000000000008</v>
@@ -4398,23 +4368,23 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B212" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A213" s="15" t="s">
-        <v>193</v>
-      </c>
-      <c r="B213" s="2">
+      <c r="A213" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="B213" s="15">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B214" s="2">
         <v>660.66000000000008</v>
@@ -4422,7 +4392,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B215" s="2">
         <v>660.66000000000008</v>
@@ -4430,7 +4400,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B216" s="2">
         <v>660.66000000000008</v>
@@ -4438,39 +4408,39 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B217" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A218" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B218" s="2">
+      <c r="A218" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B218" s="15">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B219" s="2">
+        <v>200</v>
+      </c>
+      <c r="B219" s="15">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A220" s="12" t="s">
-        <v>200</v>
-      </c>
-      <c r="B220" s="2">
+      <c r="A220" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="B220" s="15">
         <v>707.85</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B221" s="2">
         <v>660.66000000000008</v>
@@ -4478,7 +4448,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B222" s="2">
         <v>660.66000000000008</v>
@@ -4489,13 +4459,13 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A224" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B224" s="2"/>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A225" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B225" s="2">
         <v>1038.1799999999998</v>
@@ -4503,7 +4473,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A226" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B226" s="2">
         <v>1038.1799999999998</v>
@@ -4511,7 +4481,7 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A227" s="3" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B227" s="2">
         <v>1038.1799999999998</v>
@@ -4519,7 +4489,7 @@
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A228" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B228" s="2">
         <v>1038.1799999999998</v>
@@ -4527,7 +4497,7 @@
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A229" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B229" s="2">
         <v>2359.5</v>
@@ -4535,7 +4505,7 @@
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A230" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B230" s="2">
         <v>1887.6000000000001</v>
@@ -4543,7 +4513,7 @@
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A231" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B231" s="2">
         <v>1793.2200000000003</v>
@@ -4551,7 +4521,7 @@
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A232" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B232" s="2">
         <v>1793.2200000000003</v>
@@ -4559,7 +4529,7 @@
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A233" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B233" s="2">
         <v>2477.4749999999999</v>
@@ -4567,7 +4537,7 @@
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A234" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B234" s="2">
         <v>2949.375</v>
@@ -4575,7 +4545,7 @@
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A235" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B235" s="2">
         <v>2949.375</v>
@@ -4583,7 +4553,7 @@
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A236" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B236" s="2">
         <v>1793.2200000000003</v>
@@ -4591,7 +4561,7 @@
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A237" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B237" s="2">
         <v>2359.5</v>
@@ -4599,15 +4569,15 @@
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A238" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B238" s="2">
         <v>1793.2200000000003</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A239" s="7" t="s">
-        <v>218</v>
+      <c r="A239" s="8" t="s">
+        <v>219</v>
       </c>
       <c r="B239" s="2">
         <v>1132.56</v>
@@ -4615,39 +4585,39 @@
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A240" s="3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B240" s="2">
         <v>1415.7</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A241" s="7" t="s">
-        <v>220</v>
+      <c r="A241" s="8" t="s">
+        <v>221</v>
       </c>
       <c r="B241" s="2">
         <v>2005.575</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A242" s="7" t="s">
-        <v>221</v>
+      <c r="A242" s="8" t="s">
+        <v>222</v>
       </c>
       <c r="B242" s="2">
         <v>2052.7650000000003</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A243" s="7" t="s">
-        <v>222</v>
+      <c r="A243" s="8" t="s">
+        <v>223</v>
       </c>
       <c r="B243" s="2">
         <v>2359.5</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A244" s="7" t="s">
-        <v>223</v>
+      <c r="A244" s="8" t="s">
+        <v>224</v>
       </c>
       <c r="B244" s="2">
         <v>3775.2000000000003</v>
@@ -4657,12 +4627,12 @@
       <c r="B245" s="2"/>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A246" s="14"/>
+      <c r="A246" s="16"/>
       <c r="B246" s="2"/>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A247" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B247" s="2"/>
     </row>
@@ -4670,14 +4640,14 @@
       <c r="B248" s="2"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A249" s="12" t="s">
-        <v>225</v>
+      <c r="A249" s="13" t="s">
+        <v>226</v>
       </c>
       <c r="B249" s="2"/>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A250" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B250" s="2">
         <v>505.375</v>
@@ -4685,45 +4655,45 @@
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A251" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B251" s="2">
         <v>505.375</v>
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A252" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B252" s="2">
-        <v>570.375</v>
-      </c>
+      <c r="A252" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B252" s="2"/>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A253" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B253" s="2">
-        <v>570.375</v>
+        <v>589.875</v>
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A254" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B254" s="2">
-        <v>570.375</v>
+        <v>589.875</v>
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A255" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B255" s="2"/>
+      <c r="A255" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B255" s="2">
+        <v>589.875</v>
+      </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A256" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B256" s="2">
         <v>589.875</v>
@@ -4731,7 +4701,7 @@
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A257" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B257" s="2">
         <v>589.875</v>
@@ -4739,7 +4709,7 @@
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A258" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B258" s="2">
         <v>589.875</v>
@@ -4747,45 +4717,45 @@
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A259" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B259" s="2">
         <v>589.875</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A260" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="B260" s="2">
-        <v>589.875</v>
-      </c>
+      <c r="A260" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B260" s="2"/>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A261" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B261" s="2">
-        <v>589.875</v>
+        <v>661.375</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A262" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B262" s="2">
-        <v>589.875</v>
+        <v>661.375</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A263" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B263" s="2"/>
+      <c r="A263" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B263" s="2">
+        <v>661.375</v>
+      </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A264" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B264" s="2">
         <v>661.375</v>
@@ -4793,7 +4763,7 @@
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A265" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B265" s="2">
         <v>661.375</v>
@@ -4801,7 +4771,7 @@
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A266" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B266" s="2">
         <v>661.375</v>
@@ -4809,7 +4779,7 @@
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A267" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B267" s="2">
         <v>661.375</v>
@@ -4817,7 +4787,7 @@
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A268" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B268" s="2">
         <v>661.375</v>
@@ -4825,7 +4795,7 @@
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A269" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B269" s="2">
         <v>661.375</v>
@@ -4833,1261 +4803,1238 @@
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A270" s="3" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B270" s="2">
         <v>661.375</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A271" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="B271" s="2">
-        <v>661.375</v>
-      </c>
+      <c r="A271" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B271" s="2"/>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A272" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B272" s="2">
-        <v>661.375</v>
-      </c>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+        <v>846.625</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B273" s="2">
-        <v>661.375</v>
-      </c>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A274" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B274" s="2"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+        <v>846.625</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B274" s="2">
+        <v>846.625</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B275" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B276" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B277" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B278" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B279" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B280" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B281" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B282" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A283" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B283" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A284" s="3" t="s">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283" s="16" t="s">
         <v>260</v>
+      </c>
+      <c r="B283" s="2"/>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284" s="8" t="s">
+        <v>261</v>
       </c>
       <c r="B284" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A285" s="3" t="s">
-        <v>261</v>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285" s="8" t="s">
+        <v>262</v>
       </c>
       <c r="B285" s="2">
         <v>846.625</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A286" s="14" t="s">
-        <v>262</v>
-      </c>
-      <c r="B286" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A287" s="7" t="s">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B286" s="2"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287" s="1" t="s">
         <v>263</v>
       </c>
-      <c r="B287" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A288" s="7" t="s">
+      <c r="B287" s="2"/>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288" s="13" t="s">
         <v>264</v>
       </c>
-      <c r="B288" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A289" s="14" t="s">
+      <c r="B288" s="2"/>
+      <c r="G288" s="13"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A289" s="3" t="s">
         <v>265</v>
       </c>
       <c r="B289" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A290" s="7" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A290" s="3" t="s">
         <v>266</v>
       </c>
       <c r="B290" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A291" s="7" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A291" s="3" t="s">
         <v>267</v>
       </c>
       <c r="B291" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A292" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B292" s="2">
-        <v>846.625</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A293" s="12" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B292" s="2"/>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A293" s="13" t="s">
         <v>268</v>
       </c>
       <c r="B293" s="2"/>
-    </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G293" s="13"/>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B294" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A295" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B295" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A296" s="3" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B296" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A297" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B297" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A298" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B298" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A299" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B299" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A300" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B300" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A301" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B301" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B300" s="2"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A301" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B301" s="2"/>
+      <c r="G301" s="13"/>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
-        <v>254</v>
+        <v>276</v>
       </c>
       <c r="B302" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A303" s="3" t="s">
-        <v>255</v>
+        <v>277</v>
       </c>
       <c r="B303" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A304" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B304" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A305" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B305" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A306" s="3" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B306" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A307" s="3" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B307" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A308" s="3" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B308" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A309" s="3" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B309" s="2">
-        <v>1218.75</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A310" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="B310" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="A310" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B310" s="2"/>
+      <c r="G310" s="13"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B311" s="2"/>
+      <c r="A311" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="B311" s="2">
+        <v>1755</v>
+      </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A312" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B312" s="2"/>
+      <c r="A312" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B312" s="2">
+        <v>1755</v>
+      </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A313" s="3" t="s">
-        <v>251</v>
+        <v>286</v>
       </c>
       <c r="B313" s="2">
-        <v>1462.5</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A314" s="3" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B314" s="2">
-        <v>1462.5</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A315" s="3" t="s">
-        <v>259</v>
+        <v>288</v>
       </c>
       <c r="B315" s="2">
-        <v>1462.5</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A316" s="3" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B316" s="2">
-        <v>1462.5</v>
+        <v>1755</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B317" s="2"/>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A318" s="1" t="s">
-        <v>283</v>
+      <c r="A318" s="13" t="s">
+        <v>290</v>
       </c>
       <c r="B318" s="2"/>
+      <c r="G318" s="13"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A319" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B319" s="2"/>
-      <c r="G319" s="12"/>
+      <c r="A319" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="B319" s="2">
+        <v>1966.25</v>
+      </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A320" s="3" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B320" s="2">
-        <v>975</v>
+        <v>1966.25</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A321" s="3" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B321" s="2">
-        <v>975</v>
+        <v>1966.25</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A322" s="3" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="B322" s="2">
-        <v>975</v>
+        <v>1966.25</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B323" s="2"/>
+      <c r="A323" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B323" s="2">
+        <v>1966.25</v>
+      </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A324" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B324" s="2"/>
-      <c r="G324" s="12"/>
+      <c r="A324" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B324" s="2">
+        <v>1966.25</v>
+      </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A325" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B325" s="2">
-        <v>1235</v>
-      </c>
+      <c r="B325" s="2"/>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A326" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="B326" s="2">
-        <v>1235</v>
-      </c>
+      <c r="A326" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="B326" s="2"/>
+      <c r="G326" s="13"/>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="B327" s="2">
-        <v>1235</v>
+        <v>2218.125</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A328" s="3" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B328" s="2">
-        <v>1235</v>
+        <v>2218.125</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A329" s="3" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B329" s="2">
-        <v>1235</v>
+        <v>2218.125</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A330" s="3" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B330" s="2">
-        <v>1235</v>
+        <v>2218.125</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B331" s="2"/>
+      <c r="A331" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="B331" s="2">
+        <v>2218.125</v>
+      </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A332" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="B332" s="2"/>
-      <c r="G332" s="12"/>
+      <c r="A332" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B332" s="2">
+        <v>2218.125</v>
+      </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A333" s="3" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="B333" s="2">
-        <v>1495</v>
+        <v>2218.125</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A334" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B334" s="2">
-        <v>1495</v>
-      </c>
+      <c r="B334" s="2"/>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A335" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="B335" s="2">
-        <v>1495</v>
-      </c>
+      <c r="A335" s="13" t="s">
+        <v>305</v>
+      </c>
+      <c r="B335" s="2"/>
+      <c r="G335" s="13"/>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A336" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B336" s="2">
-        <v>1495</v>
-      </c>
+      <c r="B336" s="9"/>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A337" s="3" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B337" s="2">
-        <v>1495</v>
+        <v>2502.5</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A338" s="3" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B338" s="2">
-        <v>1495</v>
+        <v>1966.25</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A339" s="3" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B339" s="2">
-        <v>1495</v>
+        <v>1966.25</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A340" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B340" s="2">
-        <v>1495</v>
-      </c>
+      <c r="B340" s="2"/>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A341" s="12" t="s">
-        <v>250</v>
+      <c r="A341" s="13" t="s">
+        <v>309</v>
       </c>
       <c r="B341" s="2"/>
-      <c r="G341" s="12"/>
+      <c r="G341" s="13"/>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B342" s="2">
-        <v>1755</v>
+        <v>3038.75</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A343" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B343" s="2">
-        <v>1755</v>
+        <v>3038.75</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A344" s="3" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B344" s="2">
-        <v>1755</v>
-      </c>
+        <v>3038.75</v>
+      </c>
+      <c r="C344" s="19"/>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A345" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="B345" s="2">
-        <v>1755</v>
-      </c>
+      <c r="B345" s="2"/>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A346" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="B346" s="2">
-        <v>1755</v>
-      </c>
+      <c r="A346" s="8"/>
+      <c r="B346" s="2"/>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A347" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="B347" s="2">
-        <v>1755</v>
-      </c>
+      <c r="A347" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B347" s="2"/>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A348" s="13" t="s">
+        <v>264</v>
+      </c>
       <c r="B348" s="2"/>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A349" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B349" s="2"/>
-      <c r="G349" s="12"/>
+      <c r="A349" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="B349" s="2">
+        <v>637</v>
+      </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A350" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B350" s="2">
-        <v>1966.25</v>
+        <v>637</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A351" s="3" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="B351" s="2">
-        <v>1966.25</v>
+        <v>637</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A352" s="3" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="B352" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A353" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="B353" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A354" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B354" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A355" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="B355" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B356" s="2"/>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A357" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B357" s="2"/>
-      <c r="G357" s="12"/>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A358" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B358" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A359" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B359" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B356" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B357" s="2">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B358" s="2"/>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="B359" s="2"/>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A360" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="B360" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A361" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="B361" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A362" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B362" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A363" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B363" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A364" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="B364" s="2">
-        <v>2218.125</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B365" s="2"/>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A366" s="12" t="s">
-        <v>323</v>
-      </c>
-      <c r="B366" s="2"/>
-      <c r="G366" s="12"/>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B367" s="8"/>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B365" s="2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B366" s="2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B367" s="2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A368" s="3" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B368" s="2">
-        <v>2502.5</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A369" s="3" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="B369" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A370" s="3" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B370" s="2">
-        <v>1966.25</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B371" s="2"/>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A372" s="12" t="s">
-        <v>327</v>
-      </c>
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B371" s="2">
+        <v>771.875</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B372" s="2"/>
-      <c r="G372" s="12"/>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A373" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B373" s="2">
-        <v>3038.75</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B373" s="2"/>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A374" s="3" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B374" s="2">
-        <v>3038.75</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A375" s="3" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B375" s="2">
-        <v>3038.75</v>
-      </c>
-      <c r="C375" s="16"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B376" s="2"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A377" s="7"/>
-      <c r="B377" s="2"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A378" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="B378" s="2"/>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A379" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B379" s="2"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B376" s="2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B377" s="2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B378" s="2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="B379" s="2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A380" s="3" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="B380" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A381" s="3" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B381" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A382" s="3" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="B382" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A383" s="3" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B383" s="2">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A384" s="3" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="B384" s="2">
-        <v>637</v>
+        <v>975</v>
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A385" s="3" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B385" s="2">
-        <v>637</v>
+        <v>975</v>
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A386" s="3" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="B386" s="2">
-        <v>637</v>
+        <v>975</v>
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A387" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B387" s="2">
-        <v>637</v>
-      </c>
+      <c r="B387" s="2"/>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A388" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="B388" s="2">
-        <v>637</v>
-      </c>
+      <c r="A388" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B388" s="2"/>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B389" s="2"/>
+      <c r="A389" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="B389" s="2">
+        <v>1158.625</v>
+      </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A390" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B390" s="2"/>
+      <c r="A390" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B390" s="2">
+        <v>1158.625</v>
+      </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A391" s="3" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="B391" s="2">
-        <v>771.875</v>
+        <v>1158.625</v>
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A392" s="3" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B392" s="2">
-        <v>771.875</v>
+        <v>1158.625</v>
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A393" s="3" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B393" s="2">
-        <v>771.875</v>
+        <v>1158.625</v>
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A394" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="B394" s="2">
-        <v>771.875</v>
-      </c>
+      <c r="B394" s="2"/>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A395" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B395" s="2">
-        <v>771.875</v>
-      </c>
+      <c r="A395" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B395" s="2"/>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A396" s="3" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B396" s="2">
-        <v>771.875</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A397" s="3" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B397" s="2">
-        <v>771.875</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A398" s="3" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="B398" s="2">
-        <v>771.875</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A399" s="3" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="B399" s="2">
-        <v>771.875</v>
+        <v>1280.5</v>
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A400" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="B400" s="2">
-        <v>771.875</v>
-      </c>
+      <c r="B400" s="2"/>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A401" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="B401" s="2">
-        <v>771.875</v>
-      </c>
+      <c r="A401" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="B401" s="2"/>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A402" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B402" s="2">
-        <v>771.875</v>
-      </c>
+      <c r="A402" s="13"/>
+      <c r="B402" s="2"/>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" s="13" t="s">
+        <v>264</v>
+      </c>
       <c r="B403" s="2"/>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A404" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="B404" s="2"/>
+      <c r="A404" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B404" s="2">
+        <v>698.75</v>
+      </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A405" s="3" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B405" s="2">
-        <v>975</v>
+        <v>788.125</v>
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A406" s="3" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B406" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A407" s="3" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B407" s="2">
-        <v>975</v>
+        <v>983.125</v>
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A408" s="3" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B408" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A409" s="3" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B409" s="2">
-        <v>975</v>
+        <v>983.125</v>
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A410" s="3" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="B410" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A411" s="3" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B411" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A412" s="3" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B412" s="2">
-        <v>975</v>
+        <v>698.75</v>
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A413" s="3" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B413" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A414" s="3" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B414" s="2">
-        <v>975</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A415" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="B415" s="2">
-        <v>975</v>
-      </c>
+      <c r="B415" s="2"/>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A416" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B416" s="2">
-        <v>975</v>
-      </c>
+      <c r="A416" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B416" s="2"/>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A417" s="3" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="B417" s="2">
-        <v>975</v>
+        <v>1072.5</v>
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B418" s="2"/>
+      <c r="A418" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B418" s="2">
+        <v>1291.875</v>
+      </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A419" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B419" s="2"/>
+      <c r="A419" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B419" s="2">
+        <v>1291.875</v>
+      </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A420" s="3" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="B420" s="2">
-        <v>1158.625</v>
+        <v>1291.875</v>
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A421" s="3" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B421" s="2">
-        <v>1158.625</v>
+        <v>1291.875</v>
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A422" s="3" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="B422" s="2">
-        <v>1158.625</v>
+        <v>1291.875</v>
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A423" s="3" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B423" s="2">
-        <v>1158.625</v>
+        <v>934.375</v>
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A424" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B424" s="2">
-        <v>1158.625</v>
-      </c>
+      <c r="B424" s="2"/>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="B425" s="2"/>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A426" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B426" s="2"/>
+      <c r="A426" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B426" s="2">
+        <v>1251.25</v>
+      </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A427" s="3" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B427" s="2">
-        <v>1280.5</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A428" s="3" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B428" s="2">
-        <v>1280.5</v>
+        <v>2112.5</v>
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A429" s="3" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="B429" s="2">
-        <v>1280.5</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A430" s="3" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="B430" s="2">
-        <v>1280.5</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B431" s="2"/>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A432" s="1" t="s">
-        <v>375</v>
+      <c r="A432" s="13" t="s">
+        <v>382</v>
       </c>
       <c r="B432" s="2"/>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A433" s="12"/>
-      <c r="B433" s="2"/>
+      <c r="A433" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="B433" s="2">
+        <v>2039.375</v>
+      </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A434" s="12" t="s">
-        <v>284</v>
-      </c>
-      <c r="B434" s="2"/>
+      <c r="A434" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B434" s="2">
+        <v>2039.375</v>
+      </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A435" s="3" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="B435" s="2">
-        <v>698.75</v>
+        <v>2039.375</v>
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A436" s="3" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B436" s="2">
-        <v>788.125</v>
+        <v>2039.375</v>
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A437" s="3" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="B437" s="2">
-        <v>893.75</v>
+        <v>2039.375</v>
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A438" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B438" s="2">
-        <v>983.125</v>
-      </c>
+      <c r="B438" s="2"/>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A439" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="B439" s="2">
-        <v>893.75</v>
-      </c>
+      <c r="A439" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="B439" s="2"/>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A440" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="B440" s="2">
-        <v>983.125</v>
-      </c>
+      <c r="A440" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B440" s="2"/>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A441" s="3" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="B441" s="2">
         <v>893.75</v>
@@ -6095,7 +6042,7 @@
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A442" s="3" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="B442" s="2">
         <v>893.75</v>
@@ -6103,15 +6050,15 @@
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A443" s="3" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B443" s="2">
-        <v>698.75</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A444" s="3" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B444" s="2">
         <v>893.75</v>
@@ -6119,666 +6066,729 @@
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A445" s="3" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="B445" s="2">
         <v>893.75</v>
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B446" s="2"/>
+      <c r="A446" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="B446" s="2">
+        <v>893.75</v>
+      </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A447" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="B447" s="2"/>
+      <c r="A447" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B447" s="2">
+        <v>893.75</v>
+      </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A448" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B448" s="2">
-        <v>1072.5</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A449" s="3" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="B449" s="2">
-        <v>1291.875</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A450" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B450" s="2">
-        <v>1291.875</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A451" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B451" s="2">
-        <v>1291.875</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A452" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B452" s="2">
-        <v>1291.875</v>
+        <v>893.75</v>
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A453" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B453" s="2">
-        <v>1291.875</v>
-      </c>
+      <c r="A453" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="B453" s="2"/>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A454" s="3"/>
-      <c r="B454" s="2"/>
+      <c r="A454" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="B454" s="2">
+        <v>1056.25</v>
+      </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B455" s="2"/>
+      <c r="A455" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B455" s="2">
+        <v>1056.25</v>
+      </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A456" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B456" s="2"/>
+      <c r="A456" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="B456" s="2">
+        <v>1056.25</v>
+      </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A457" s="3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B457" s="2">
-        <v>1251.25</v>
+        <v>1056.25</v>
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A458" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B458" s="2">
-        <v>1950</v>
+        <v>1056.25</v>
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A459" s="3" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="B459" s="2">
-        <v>2112.5</v>
+        <v>1056.25</v>
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A460" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B460" s="2">
-        <v>1950</v>
+        <v>1056.25</v>
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A461" s="3" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B461" s="2">
-        <v>1950</v>
+        <v>1056.25</v>
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B462" s="2"/>
+      <c r="A462" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B462" s="2">
+        <v>1056.25</v>
+      </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A463" s="12" t="s">
-        <v>399</v>
-      </c>
       <c r="B463" s="2"/>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A464" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="B464" s="2">
-        <v>2039.375</v>
-      </c>
+      <c r="B464" s="2"/>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A465" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B465" s="2">
-        <v>2039.375</v>
-      </c>
+      <c r="A465" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B465" s="2"/>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A466" s="3" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="B466" s="2">
-        <v>2039.375</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A467" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B467" s="2">
-        <v>2039.375</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A468" s="3" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="B468" s="2">
-        <v>2039.375</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B469" s="2"/>
+      <c r="A469" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B469" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A470" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="B470" s="2"/>
+      <c r="A470" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B470" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A471" s="13"/>
-      <c r="B471" s="2"/>
+      <c r="A471" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B471" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A472" s="12" t="s">
-        <v>225</v>
-      </c>
+      <c r="A472" s="3"/>
       <c r="B472" s="2"/>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A473" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B473" s="2">
-        <v>893.75</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A474" s="3" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="B474" s="2">
-        <v>893.75</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A475" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B475" s="2">
-        <v>893.75</v>
-      </c>
+      <c r="B475" s="2"/>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A476" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="B476" s="2">
-        <v>893.75</v>
-      </c>
+      <c r="A476" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B476" s="2"/>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A477" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="B477" s="2">
-        <v>893.75</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A478" s="3" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B478" s="2">
-        <v>893.75</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A479" s="3" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="B479" s="2">
-        <v>893.75</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A480" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="B480" s="2">
-        <v>893.75</v>
-      </c>
-    </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A481" s="3" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B481" s="2">
-        <v>893.75</v>
-      </c>
-    </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A482" s="3" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="B482" s="2">
-        <v>893.75</v>
-      </c>
-    </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A483" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="B483" s="2">
-        <v>893.75</v>
-      </c>
-    </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A484" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="B484" s="2">
-        <v>893.75</v>
-      </c>
-    </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A485" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="B485" s="2"/>
-    </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A484" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="B484" s="2"/>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A485" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="B485" s="2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A486" s="3" t="s">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="B486" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A487" s="3" t="s">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="B487" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A488" s="3" t="s">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B488" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A489" s="3" t="s">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="B489" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A490" s="3" t="s">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="B490" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+      <c r="D490" s="3"/>
+    </row>
+    <row r="491" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A491" s="3" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="B491" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="492" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A492" s="3" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B492" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A493" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="B493" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1381.25</v>
+      </c>
+    </row>
+    <row r="493" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A493" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="B493" s="2"/>
+    </row>
+    <row r="494" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A494" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B494" s="2">
-        <v>1056.25</v>
-      </c>
-    </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B495" s="2"/>
-    </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B496" s="2"/>
+        <v>1686.75</v>
+      </c>
+    </row>
+    <row r="495" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A495" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="B495" s="2">
+        <v>1686.75</v>
+      </c>
+    </row>
+    <row r="496" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A496" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="B496" s="2">
+        <v>1686.75</v>
+      </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B497" s="2"/>
+      <c r="A497" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="B497" s="2">
+        <v>1686.75</v>
+      </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B498" s="2"/>
+      <c r="A498" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B498" s="2">
+        <v>1686.75</v>
+      </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B499" s="2"/>
+      <c r="A499" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="B499" s="2">
+        <v>1686.75</v>
+      </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B500" s="2"/>
+      <c r="A500" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B500" s="2">
+        <v>1686.75</v>
+      </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B501" s="2"/>
+      <c r="A501" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="B501" s="20"/>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A502" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="B502" s="2"/>
+      <c r="A502" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="B502" s="2">
+        <v>660.66000000000008</v>
+      </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A503" s="3" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="B503" s="2">
-        <v>1218.75</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A504" s="3" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="B504" s="2">
-        <v>1218.75</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A505" s="3" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="B505" s="2">
-        <v>1218.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A506" s="3" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="B506" s="2">
-        <v>1218.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A507" s="3" t="s">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c r="B507" s="2">
-        <v>1218.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A508" s="3" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="B508" s="2">
-        <v>1218.75</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A509" s="3"/>
-      <c r="B509" s="2"/>
+      <c r="A509" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="B509" s="2">
+        <v>660.66000000000008</v>
+      </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A510" s="3" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="B510" s="2">
-        <v>1218.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A511" s="3" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
       <c r="B511" s="2">
-        <v>1218.75</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B512" s="2"/>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A513" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="B513" s="2"/>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A512" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B512" s="2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A513" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="B513" s="2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A514" s="3" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B514" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A515" s="3" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="B515" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A516" s="3" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="B516" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A517" s="3" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="B517" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A518" s="3" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="B518" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A519" s="3" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="B519" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A520" s="3" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="B520" s="2">
-        <v>1300</v>
-      </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A521" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="B521" s="2"/>
-    </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A521" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="B521" s="2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A522" s="3" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="B522" s="2">
-        <v>1381.25</v>
-      </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A523" s="3" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="B523" s="2">
-        <v>1381.25</v>
-      </c>
-    </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A524" s="3" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="B524" s="2">
-        <v>1381.25</v>
-      </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A525" s="3" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="B525" s="2">
-        <v>1381.25</v>
-      </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A526" s="3" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="B526" s="2">
-        <v>1381.25</v>
-      </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A527" s="3" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="B527" s="2">
-        <v>1381.25</v>
-      </c>
-      <c r="D527" s="3"/>
-    </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A528" s="3" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B528" s="2">
-        <v>1381.25</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A529" s="3" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="B529" s="2">
-        <v>1381.25</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A530" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="B530" s="2"/>
+      <c r="A530" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B530" s="2">
+        <v>755.04</v>
+      </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A531" s="3" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="B531" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A532" s="3" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="B532" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A533" s="3" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="B533" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A534" s="3" t="s">
-        <v>452</v>
+        <v>471</v>
       </c>
       <c r="B534" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A535" s="3" t="s">
-        <v>453</v>
+        <v>472</v>
       </c>
       <c r="B535" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A536" s="3" t="s">
-        <v>454</v>
+        <v>473</v>
       </c>
       <c r="B536" s="2">
-        <v>1686.75</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A537" s="3" t="s">
-        <v>455</v>
+        <v>474</v>
       </c>
       <c r="B537" s="2">
-        <v>1686.75</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A538" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="B538" s="17"/>
+      <c r="A538" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B538" s="2">
+        <v>660.66000000000008</v>
+      </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A539" s="3" t="s">
-        <v>457</v>
+        <v>476</v>
       </c>
       <c r="B539" s="2">
         <v>660.66000000000008</v>
@@ -6786,23 +6796,23 @@
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A540" s="3" t="s">
-        <v>458</v>
+        <v>477</v>
       </c>
       <c r="B540" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A541" s="3" t="s">
-        <v>458</v>
+        <v>478</v>
       </c>
       <c r="B541" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A542" s="3" t="s">
-        <v>459</v>
+        <v>479</v>
       </c>
       <c r="B542" s="2">
         <v>660.66000000000008</v>
@@ -6810,7 +6820,7 @@
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A543" s="3" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="B543" s="2">
         <v>660.66000000000008</v>
@@ -6818,7 +6828,7 @@
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A544" s="3" t="s">
-        <v>461</v>
+        <v>481</v>
       </c>
       <c r="B544" s="2">
         <v>660.66000000000008</v>
@@ -6826,23 +6836,23 @@
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A545" s="3" t="s">
-        <v>462</v>
+        <v>482</v>
       </c>
       <c r="B545" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A546" s="3" t="s">
-        <v>463</v>
+        <v>483</v>
       </c>
       <c r="B546" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A547" s="3" t="s">
-        <v>464</v>
+      <c r="A547" s="1" t="s">
+        <v>484</v>
       </c>
       <c r="B547" s="2">
         <v>660.66000000000008</v>
@@ -6850,23 +6860,23 @@
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A548" s="3" t="s">
-        <v>465</v>
+        <v>485</v>
       </c>
       <c r="B548" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A549" s="3" t="s">
-        <v>466</v>
+        <v>486</v>
       </c>
       <c r="B549" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A550" s="3" t="s">
-        <v>467</v>
+        <v>487</v>
       </c>
       <c r="B550" s="2">
         <v>660.66000000000008</v>
@@ -6874,7 +6884,7 @@
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A551" s="3" t="s">
-        <v>468</v>
+        <v>488</v>
       </c>
       <c r="B551" s="2">
         <v>660.66000000000008</v>
@@ -6882,15 +6892,15 @@
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A552" s="3" t="s">
-        <v>469</v>
+        <v>489</v>
       </c>
       <c r="B552" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A553" s="3" t="s">
-        <v>470</v>
+        <v>490</v>
       </c>
       <c r="B553" s="2">
         <v>660.66000000000008</v>
@@ -6898,7 +6908,7 @@
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A554" s="3" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="B554" s="2">
         <v>660.66000000000008</v>
@@ -6906,15 +6916,15 @@
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A555" s="3" t="s">
-        <v>472</v>
+        <v>492</v>
       </c>
       <c r="B555" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A556" s="3" t="s">
-        <v>473</v>
+        <v>493</v>
       </c>
       <c r="B556" s="2">
         <v>660.66000000000008</v>
@@ -6922,7 +6932,7 @@
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A557" s="3" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="B557" s="2">
         <v>660.66000000000008</v>
@@ -6930,7 +6940,7 @@
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A558" s="3" t="s">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="B558" s="2">
         <v>660.66000000000008</v>
@@ -6938,7 +6948,7 @@
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A559" s="3" t="s">
-        <v>476</v>
+        <v>496</v>
       </c>
       <c r="B559" s="2">
         <v>660.66000000000008</v>
@@ -6946,7 +6956,7 @@
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A560" s="3" t="s">
-        <v>477</v>
+        <v>497</v>
       </c>
       <c r="B560" s="2">
         <v>660.66000000000008</v>
@@ -6954,7 +6964,7 @@
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A561" s="3" t="s">
-        <v>478</v>
+        <v>498</v>
       </c>
       <c r="B561" s="2">
         <v>660.66000000000008</v>
@@ -6962,7 +6972,7 @@
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A562" s="3" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="B562" s="2">
         <v>660.66000000000008</v>
@@ -6970,7 +6980,7 @@
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A563" s="3" t="s">
-        <v>480</v>
+        <v>500</v>
       </c>
       <c r="B563" s="2">
         <v>660.66000000000008</v>
@@ -6978,15 +6988,15 @@
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A564" s="3" t="s">
-        <v>481</v>
+        <v>501</v>
       </c>
       <c r="B564" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A565" s="3" t="s">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B565" s="2">
         <v>660.66000000000008</v>
@@ -6994,7 +7004,7 @@
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A566" s="3" t="s">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="B566" s="2">
         <v>660.66000000000008</v>
@@ -7002,15 +7012,15 @@
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A567" s="3" t="s">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="B567" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A568" s="3" t="s">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="B568" s="2">
         <v>660.66000000000008</v>
@@ -7018,7 +7028,7 @@
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A569" s="3" t="s">
-        <v>486</v>
+        <v>506</v>
       </c>
       <c r="B569" s="2">
         <v>660.66000000000008</v>
@@ -7026,23 +7036,20 @@
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A570" s="3" t="s">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="B570" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A571" s="3" t="s">
-        <v>488</v>
-      </c>
       <c r="B571" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A572" s="3" t="s">
-        <v>489</v>
+      <c r="A572" s="1" t="s">
+        <v>508</v>
       </c>
       <c r="B572" s="2">
         <v>660.66000000000008</v>
@@ -7050,15 +7057,15 @@
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A573" s="3" t="s">
-        <v>490</v>
+        <v>509</v>
       </c>
       <c r="B573" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A574" s="3" t="s">
-        <v>491</v>
+        <v>510</v>
       </c>
       <c r="B574" s="2">
         <v>660.66000000000008</v>
@@ -7066,159 +7073,154 @@
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A575" s="3" t="s">
-        <v>492</v>
+        <v>511</v>
       </c>
       <c r="B575" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A576" s="3" t="s">
-        <v>493</v>
+        <v>512</v>
       </c>
       <c r="B576" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A577" s="3" t="s">
-        <v>494</v>
+        <v>513</v>
       </c>
       <c r="B577" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A578" s="3" t="s">
-        <v>495</v>
+        <v>514</v>
       </c>
       <c r="B578" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A579" s="3" t="s">
-        <v>496</v>
+        <v>57</v>
       </c>
       <c r="B579" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A580" s="3" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="B580" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A581" s="3" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B581" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A582" s="3" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="B582" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A583" s="3" t="s">
-        <v>500</v>
-      </c>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B583" s="2">
-        <v>755.04</v>
-      </c>
-    </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A584" s="1" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="B584" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A585" s="3" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="B585" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A586" s="3" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="B586" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A587" s="3" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="B587" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A588" s="3" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="B588" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A589" s="3" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
       <c r="B589" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A590" s="3" t="s">
-        <v>507</v>
-      </c>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B590" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A591" s="3" t="s">
-        <v>508</v>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A591" s="1" t="s">
+        <v>524</v>
       </c>
       <c r="B591" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A592" s="3" t="s">
-        <v>509</v>
+        <v>525</v>
       </c>
       <c r="B592" s="2">
         <v>660.66000000000008</v>
       </c>
+      <c r="C592" s="3"/>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A593" s="3" t="s">
-        <v>510</v>
+        <v>526</v>
       </c>
       <c r="B593" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A594" s="3" t="s">
-        <v>511</v>
+        <v>527</v>
       </c>
       <c r="B594" s="2">
         <v>660.66000000000008</v>
@@ -7226,7 +7228,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A595" s="3" t="s">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="B595" s="2">
         <v>660.66000000000008</v>
@@ -7234,7 +7236,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A596" s="3" t="s">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="B596" s="2">
         <v>660.66000000000008</v>
@@ -7242,15 +7244,15 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A597" s="3" t="s">
-        <v>514</v>
+        <v>530</v>
       </c>
       <c r="B597" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A598" s="3" t="s">
-        <v>515</v>
+        <v>531</v>
       </c>
       <c r="B598" s="2">
         <v>660.66000000000008</v>
@@ -7258,7 +7260,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A599" s="3" t="s">
-        <v>516</v>
+        <v>532</v>
       </c>
       <c r="B599" s="2">
         <v>660.66000000000008</v>
@@ -7266,15 +7268,15 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A600" s="3" t="s">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="B600" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A601" s="3" t="s">
-        <v>518</v>
+        <v>534</v>
       </c>
       <c r="B601" s="2">
         <v>660.66000000000008</v>
@@ -7282,7 +7284,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A602" s="3" t="s">
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="B602" s="2">
         <v>660.66000000000008</v>
@@ -7290,15 +7292,15 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A603" s="3" t="s">
-        <v>520</v>
+        <v>536</v>
       </c>
       <c r="B603" s="2">
-        <v>660.66000000000008</v>
+        <v>755.04</v>
       </c>
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A604" s="3" t="s">
-        <v>521</v>
+        <v>537</v>
       </c>
       <c r="B604" s="2">
         <v>660.66000000000008</v>
@@ -7306,7 +7308,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A605" s="3" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
       <c r="B605" s="2">
         <v>660.66000000000008</v>
@@ -7314,7 +7316,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A606" s="3" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
       <c r="B606" s="2">
         <v>660.66000000000008</v>
@@ -7322,7 +7324,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A607" s="3" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
       <c r="B607" s="2">
         <v>660.66000000000008</v>
@@ -7335,7 +7337,7 @@
     </row>
     <row r="609" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A609" s="1" t="s">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="B609" s="2">
         <v>660.66000000000008</v>
@@ -7343,7 +7345,7 @@
     </row>
     <row r="610" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A610" s="3" t="s">
-        <v>526</v>
+        <v>542</v>
       </c>
       <c r="B610" s="2">
         <v>660.66000000000008</v>
@@ -7351,7 +7353,7 @@
     </row>
     <row r="611" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A611" s="3" t="s">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B611" s="2">
         <v>660.66000000000008</v>
@@ -7359,15 +7361,15 @@
     </row>
     <row r="612" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A612" s="3" t="s">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B612" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="613" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A613" s="3" t="s">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="B613" s="2">
         <v>660.66000000000008</v>
@@ -7375,15 +7377,15 @@
     </row>
     <row r="614" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A614" s="3" t="s">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B614" s="2">
-        <v>755.04</v>
+        <v>660.66000000000008</v>
       </c>
     </row>
     <row r="615" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A615" s="3" t="s">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="B615" s="2">
         <v>660.66000000000008</v>
@@ -7391,7 +7393,7 @@
     </row>
     <row r="616" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A616" s="3" t="s">
-        <v>56</v>
+        <v>548</v>
       </c>
       <c r="B616" s="2">
         <v>660.66000000000008</v>
@@ -7399,7 +7401,7 @@
     </row>
     <row r="617" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A617" s="3" t="s">
-        <v>532</v>
+        <v>549</v>
       </c>
       <c r="B617" s="2">
         <v>660.66000000000008</v>
@@ -7407,7 +7409,7 @@
     </row>
     <row r="618" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A618" s="3" t="s">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="B618" s="2">
         <v>660.66000000000008</v>
@@ -7415,20 +7417,23 @@
     </row>
     <row r="619" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A619" s="3" t="s">
-        <v>534</v>
+        <v>551</v>
       </c>
       <c r="B619" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A620" s="3" t="s">
+        <v>552</v>
+      </c>
       <c r="B620" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
     <row r="621" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A621" s="1" t="s">
-        <v>535</v>
+      <c r="A621" s="3" t="s">
+        <v>553</v>
       </c>
       <c r="B621" s="2">
         <v>660.66000000000008</v>
@@ -7436,7 +7441,7 @@
     </row>
     <row r="622" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A622" s="3" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="B622" s="2">
         <v>660.66000000000008</v>
@@ -7444,7 +7449,7 @@
     </row>
     <row r="623" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A623" s="3" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="B623" s="2">
         <v>660.66000000000008</v>
@@ -7452,1020 +7457,1011 @@
     </row>
     <row r="624" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A624" s="3" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="B624" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A625" s="3" t="s">
-        <v>539</v>
+        <v>199</v>
       </c>
       <c r="B625" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A626" s="3" t="s">
-        <v>540</v>
+        <v>557</v>
       </c>
       <c r="B626" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A627" s="3" t="s">
+        <v>558</v>
+      </c>
       <c r="B627" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A628" s="1" t="s">
-        <v>541</v>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A628" s="3" t="s">
+        <v>559</v>
       </c>
       <c r="B628" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.2">
+        <v>755.04</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A629" s="3" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="B629" s="2">
         <v>660.66000000000008</v>
       </c>
-      <c r="C629" s="3"/>
-    </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.2">
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A630" s="3" t="s">
-        <v>543</v>
+        <v>347</v>
       </c>
       <c r="B630" s="2">
+        <v>660.66000000000008</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A631" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B631" s="2">
         <v>755.04</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A631" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="B631" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A632" s="3" t="s">
-        <v>545</v>
+        <v>562</v>
       </c>
       <c r="B632" s="2">
         <v>660.66000000000008</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A633" s="3" t="s">
-        <v>546</v>
-      </c>
-      <c r="B633" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A634" s="3" t="s">
-        <v>547</v>
-      </c>
-      <c r="B634" s="2">
-        <v>755.04</v>
-      </c>
-    </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A635" s="3" t="s">
-        <v>548</v>
-      </c>
-      <c r="B635" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B633" s="2"/>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A634" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="B634" s="2"/>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A635" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B635" s="2"/>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A636" s="3" t="s">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="B636" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.2">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A637" s="3" t="s">
-        <v>550</v>
-      </c>
-      <c r="B637" s="2">
-        <v>755.04</v>
-      </c>
-    </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A638" s="3" t="s">
-        <v>551</v>
-      </c>
-      <c r="B638" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A639" s="3" t="s">
-        <v>552</v>
-      </c>
-      <c r="B639" s="2">
-        <v>660.66000000000008</v>
-      </c>
-    </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.2">
+        <v>565</v>
+      </c>
+      <c r="B637" s="2"/>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B638" s="2"/>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A639" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B639" s="2"/>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" s="3" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="B640" s="2">
-        <v>755.04</v>
+        <v>2905.5</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="3" t="s">
-        <v>554</v>
+        <v>567</v>
       </c>
       <c r="B641" s="2">
-        <v>660.66000000000008</v>
+        <v>2905.5</v>
       </c>
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" s="3" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="B642" s="2">
-        <v>660.66000000000008</v>
+        <v>2905.5</v>
       </c>
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A643" s="3" t="s">
-        <v>556</v>
+        <v>479</v>
       </c>
       <c r="B643" s="2">
-        <v>660.66000000000008</v>
+        <v>2905.5</v>
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A644" s="3" t="s">
-        <v>557</v>
-      </c>
-      <c r="B644" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="A644" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B644" s="2"/>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A645" s="3" t="s">
+        <v>569</v>
+      </c>
       <c r="B645" s="2">
-        <v>660.66000000000008</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A646" s="1" t="s">
-        <v>558</v>
+      <c r="A646" s="3" t="s">
+        <v>570</v>
       </c>
       <c r="B646" s="2">
-        <v>660.66000000000008</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="3" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="B647" s="2">
-        <v>660.66000000000008</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A648" s="3" t="s">
-        <v>560</v>
-      </c>
-      <c r="B648" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="B648" s="2"/>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A649" s="3" t="s">
-        <v>561</v>
-      </c>
-      <c r="B649" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="A649" s="13" t="s">
+        <v>572</v>
+      </c>
+      <c r="B649" s="2"/>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" s="3" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="B650" s="2">
-        <v>660.66000000000008</v>
+        <v>3859.375</v>
       </c>
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="3" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="B651" s="2">
-        <v>660.66000000000008</v>
+        <v>3859.375</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A652" s="3" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="B652" s="2">
-        <v>660.66000000000008</v>
+        <v>3859.375</v>
       </c>
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A653" s="3" t="s">
-        <v>565</v>
-      </c>
-      <c r="B653" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="B653" s="2"/>
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A654" s="3" t="s">
-        <v>566</v>
-      </c>
-      <c r="B654" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="A654" s="13" t="s">
+        <v>576</v>
+      </c>
+      <c r="B654" s="2"/>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="3" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B655" s="2">
-        <v>660.66000000000008</v>
+        <v>4671.875</v>
       </c>
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="3" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="B656" s="2">
-        <v>660.66000000000008</v>
+        <v>4671.875</v>
       </c>
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="3" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="B657" s="2">
-        <v>660.66000000000008</v>
+        <v>4671.875</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A658" s="3" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B658" s="2">
-        <v>660.66000000000008</v>
+        <v>4671.875</v>
       </c>
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A659" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="B659" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="B659" s="2"/>
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A660" s="3" t="s">
-        <v>572</v>
-      </c>
-      <c r="B660" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="A660" s="13" t="s">
+        <v>581</v>
+      </c>
+      <c r="B660" s="2"/>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="3" t="s">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="B661" s="2">
-        <v>660.66000000000008</v>
+        <v>7312.5</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A662" s="3" t="s">
-        <v>198</v>
+        <v>583</v>
       </c>
       <c r="B662" s="2">
-        <v>660.66000000000008</v>
+        <v>7312.5</v>
       </c>
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A663" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="B663" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="B663" s="2"/>
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A664" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="B664" s="2">
-        <v>660.66000000000008</v>
-      </c>
+      <c r="A664" s="1" t="s">
+        <v>584</v>
+      </c>
+      <c r="B664" s="2"/>
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A665" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="B665" s="2">
-        <v>755.04</v>
-      </c>
+      <c r="A665" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="B665" s="2"/>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="3" t="s">
-        <v>577</v>
+        <v>585</v>
       </c>
       <c r="B666" s="2">
-        <v>660.66000000000008</v>
+        <v>406.25</v>
       </c>
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="3" t="s">
-        <v>365</v>
+        <v>586</v>
       </c>
       <c r="B667" s="2">
-        <v>660.66000000000008</v>
+        <v>406.25</v>
       </c>
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="3" t="s">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B668" s="2">
-        <v>755.04</v>
+        <v>406.25</v>
       </c>
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="3" t="s">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B669" s="2">
-        <v>660.66000000000008</v>
+        <v>406.25</v>
       </c>
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B670" s="2"/>
+      <c r="A670" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B670" s="2">
+        <v>406.25</v>
+      </c>
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A671" s="1" t="s">
-        <v>580</v>
-      </c>
-      <c r="B671" s="2"/>
+      <c r="A671" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B671" s="2">
+        <v>406.25</v>
+      </c>
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A672" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="B672" s="2"/>
+      <c r="A672" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B672" s="2">
+        <v>406.25</v>
+      </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A673" s="3" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
       <c r="B673" s="2">
-        <v>1625</v>
+        <v>406.25</v>
       </c>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A674" s="3" t="s">
-        <v>582</v>
-      </c>
       <c r="B674" s="2"/>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A675" s="13" t="s">
+        <v>268</v>
+      </c>
       <c r="B675" s="2"/>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A676" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B676" s="2"/>
+      <c r="A676" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="B676" s="2">
+        <v>549.25</v>
+      </c>
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" s="3" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="B677" s="2">
-        <v>2905.5</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" s="3" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="B678" s="2">
-        <v>2905.5</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="3" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B679" s="2">
-        <v>2905.5</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="3" t="s">
-        <v>496</v>
+        <v>597</v>
       </c>
       <c r="B680" s="2">
-        <v>2905.5</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A681" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="B681" s="2"/>
+      <c r="A681" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="B681" s="2">
+        <v>549.25</v>
+      </c>
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" s="3" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="B682" s="2">
-        <v>3250</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="3" t="s">
-        <v>587</v>
+        <v>600</v>
       </c>
       <c r="B683" s="2">
-        <v>3250</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" s="3" t="s">
-        <v>588</v>
+        <v>601</v>
       </c>
       <c r="B684" s="2">
-        <v>3250</v>
+        <v>549.25</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B685" s="2"/>
+      <c r="A685" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B685" s="2">
+        <v>549.25</v>
+      </c>
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A686" s="12" t="s">
-        <v>589</v>
-      </c>
       <c r="B686" s="2"/>
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A687" s="3" t="s">
-        <v>590</v>
-      </c>
-      <c r="B687" s="2">
-        <v>3859.375</v>
-      </c>
+      <c r="A687" s="13" t="s">
+        <v>603</v>
+      </c>
+      <c r="B687" s="2"/>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="3" t="s">
-        <v>591</v>
+        <v>604</v>
       </c>
       <c r="B688" s="2">
-        <v>3859.375</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="3" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="B689" s="2">
-        <v>3859.375</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B690" s="2"/>
+      <c r="A690" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="B690" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A691" s="12" t="s">
-        <v>593</v>
-      </c>
-      <c r="B691" s="2"/>
+      <c r="A691" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="B691" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="3" t="s">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="B692" s="2">
-        <v>4671.875</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="3" t="s">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="B693" s="2">
-        <v>4671.875</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="3" t="s">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="B694" s="2">
-        <v>4671.875</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="3" t="s">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B695" s="2">
-        <v>4671.875</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B696" s="2"/>
+      <c r="A696" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="B696" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A697" s="12" t="s">
-        <v>598</v>
-      </c>
-      <c r="B697" s="2"/>
+      <c r="A697" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B697" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>599</v>
+        <v>172</v>
       </c>
       <c r="B698" s="2">
-        <v>7312.5</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="3" t="s">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="B699" s="2">
-        <v>7312.5</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B700" s="2"/>
+      <c r="A700" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B700" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A701" s="1" t="s">
-        <v>601</v>
-      </c>
-      <c r="B701" s="2"/>
+      <c r="A701" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B701" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A702" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="B702" s="2"/>
+      <c r="A702" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B702" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="3" t="s">
-        <v>602</v>
+        <v>507</v>
       </c>
       <c r="B703" s="2">
-        <v>406.25</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A704" s="3" t="s">
-        <v>603</v>
+        <v>618</v>
       </c>
       <c r="B704" s="2">
-        <v>406.25</v>
+        <v>690.625</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A705" s="3" t="s">
-        <v>604</v>
-      </c>
-      <c r="B705" s="2">
-        <v>406.25</v>
-      </c>
+      <c r="B705" s="2"/>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A706" s="3" t="s">
-        <v>605</v>
-      </c>
-      <c r="B706" s="2">
-        <v>406.25</v>
-      </c>
+      <c r="A706" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B706" s="2"/>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="3" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="B707" s="2">
-        <v>406.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="3" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="B708" s="2">
-        <v>406.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="3" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="B709" s="2">
-        <v>406.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" s="3" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="B710" s="2">
-        <v>406.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B711" s="2"/>
+      <c r="A711" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="B711" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A712" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="B712" s="2"/>
+      <c r="A712" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="B712" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" s="3" t="s">
-        <v>610</v>
+        <v>625</v>
       </c>
       <c r="B713" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>611</v>
+        <v>626</v>
       </c>
       <c r="B714" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" s="3" t="s">
-        <v>612</v>
+        <v>168</v>
       </c>
       <c r="B715" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="3" t="s">
-        <v>613</v>
+        <v>627</v>
       </c>
       <c r="B716" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" s="3" t="s">
-        <v>614</v>
+        <v>628</v>
       </c>
       <c r="B717" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A718" s="3" t="s">
-        <v>615</v>
+        <v>164</v>
       </c>
       <c r="B718" s="2">
-        <v>549.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A719" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="B719" s="2">
-        <v>549.25</v>
-      </c>
+      <c r="B719" s="2"/>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A720" s="3" t="s">
-        <v>617</v>
-      </c>
-      <c r="B720" s="2">
-        <v>549.25</v>
-      </c>
+      <c r="A720" s="13" t="s">
+        <v>629</v>
+      </c>
+      <c r="B720" s="2"/>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A721" s="3" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="B721" s="2">
-        <v>549.25</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="B722" s="2">
-        <v>549.25</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B723" s="2"/>
+      <c r="A723" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="B723" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A724" s="12" t="s">
-        <v>620</v>
-      </c>
-      <c r="B724" s="2"/>
+      <c r="A724" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="B724" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A725" s="3" t="s">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="B725" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A726" s="3" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
       <c r="B726" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A727" s="3" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="B727" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A728" s="3" t="s">
-        <v>624</v>
+        <v>637</v>
       </c>
       <c r="B728" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A729" s="3" t="s">
-        <v>625</v>
+        <v>638</v>
       </c>
       <c r="B729" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A730" s="3" t="s">
-        <v>626</v>
+        <v>639</v>
       </c>
       <c r="B730" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A731" s="3" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="B731" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A732" s="3" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="B732" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A733" s="3" t="s">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="B733" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A734" s="3" t="s">
-        <v>630</v>
+        <v>159</v>
       </c>
       <c r="B734" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A735" s="3" t="s">
-        <v>171</v>
+        <v>643</v>
       </c>
       <c r="B735" s="2">
-        <v>690.625</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="736" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A736" s="3" t="s">
-        <v>631</v>
-      </c>
-      <c r="B736" s="2">
-        <v>690.625</v>
-      </c>
+      <c r="B736" s="2"/>
     </row>
     <row r="737" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A737" s="3" t="s">
-        <v>632</v>
-      </c>
-      <c r="B737" s="2">
-        <v>690.625</v>
-      </c>
+      <c r="A737" s="13" t="s">
+        <v>644</v>
+      </c>
+      <c r="B737" s="2"/>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="3" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="B738" s="2">
-        <v>690.625</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" s="3" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="B739" s="2">
-        <v>690.625</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="3" t="s">
-        <v>524</v>
+        <v>647</v>
       </c>
       <c r="B740" s="2">
-        <v>690.625</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="3" t="s">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="B741" s="2">
-        <v>690.625</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B742" s="2"/>
+      <c r="A742" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="B742" s="2">
+        <v>1828.125</v>
+      </c>
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A743" s="12" t="s">
-        <v>399</v>
-      </c>
-      <c r="B743" s="2"/>
+      <c r="A743" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B743" s="2">
+        <v>1828.125</v>
+      </c>
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>636</v>
+        <v>651</v>
       </c>
       <c r="B744" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="3" t="s">
-        <v>637</v>
+        <v>652</v>
       </c>
       <c r="B745" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>638</v>
+        <v>653</v>
       </c>
       <c r="B746" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="3" t="s">
-        <v>639</v>
+        <v>654</v>
       </c>
       <c r="B747" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="3" t="s">
-        <v>640</v>
+        <v>655</v>
       </c>
       <c r="B748" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="3" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="B749" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="3" t="s">
-        <v>642</v>
+        <v>657</v>
       </c>
       <c r="B750" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="3" t="s">
-        <v>643</v>
+        <v>658</v>
       </c>
       <c r="B751" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A752" s="3" t="s">
-        <v>167</v>
+        <v>659</v>
       </c>
       <c r="B752" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="753" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A753" s="3" t="s">
-        <v>644</v>
-      </c>
-      <c r="B753" s="2">
-        <v>812.5</v>
-      </c>
+      <c r="B753" s="2"/>
     </row>
     <row r="754" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A754" s="3" t="s">
-        <v>645</v>
-      </c>
-      <c r="B754" s="2">
-        <v>812.5</v>
-      </c>
+      <c r="A754" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="B754" s="2"/>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="3" t="s">
-        <v>163</v>
+        <v>661</v>
       </c>
       <c r="B755" s="2">
         <v>812.5</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B756" s="2"/>
+      <c r="A756" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="B756" s="2">
+        <v>1828.125</v>
+      </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A757" s="12" t="s">
-        <v>646</v>
-      </c>
-      <c r="B757" s="2"/>
+      <c r="A757" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B757" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="3" t="s">
-        <v>647</v>
+        <v>663</v>
       </c>
       <c r="B758" s="2">
-        <v>1218.75</v>
+        <v>2096.25</v>
       </c>
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" s="3" t="s">
-        <v>648</v>
+        <v>664</v>
       </c>
       <c r="B759" s="2">
-        <v>1218.75</v>
+        <v>2096.25</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="3" t="s">
-        <v>649</v>
+        <v>665</v>
       </c>
       <c r="B760" s="2">
-        <v>1218.75</v>
+        <v>3152.5</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="3" t="s">
-        <v>650</v>
+        <v>666</v>
       </c>
       <c r="B761" s="2">
         <v>1218.75</v>
@@ -8473,1137 +8469,855 @@
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A762" s="3" t="s">
-        <v>651</v>
+        <v>667</v>
       </c>
       <c r="B762" s="2">
-        <v>1218.75</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A763" s="3" t="s">
-        <v>652</v>
-      </c>
-      <c r="B763" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="B763" s="2"/>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A764" s="3" t="s">
-        <v>653</v>
-      </c>
-      <c r="B764" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="B764" s="2"/>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A765" s="3" t="s">
-        <v>654</v>
-      </c>
-      <c r="B765" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="A765" s="19" t="s">
+        <v>668</v>
+      </c>
+      <c r="B765" s="2"/>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" s="3" t="s">
-        <v>655</v>
+        <v>669</v>
       </c>
       <c r="B766" s="2">
-        <v>1218.75</v>
+        <v>786.5</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="3" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="B767" s="2">
-        <v>1218.75</v>
+        <v>1085.3700000000001</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A768" s="3" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="B768" s="2">
-        <v>1218.75</v>
+        <v>1085.3700000000001</v>
       </c>
     </row>
     <row r="769" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A769" s="3" t="s">
-        <v>658</v>
-      </c>
-      <c r="B769" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="B769" s="2"/>
     </row>
     <row r="770" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A770" s="3" t="s">
-        <v>659</v>
-      </c>
-      <c r="B770" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="A770" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="B770" s="2"/>
     </row>
     <row r="771" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A771" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="B771" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="A771" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="B771" s="2"/>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A772" s="3" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="B772" s="2">
-        <v>1218.75</v>
+        <v>446.875</v>
       </c>
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B773" s="2"/>
+      <c r="A773" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="B773" s="2">
+        <v>446.875</v>
+      </c>
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A774" s="12" t="s">
-        <v>661</v>
-      </c>
-      <c r="B774" s="2"/>
+      <c r="A774" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="B774" s="2">
+        <v>446.875</v>
+      </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A775" s="3" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="B775" s="2">
-        <v>1828.125</v>
+        <v>446.875</v>
       </c>
     </row>
     <row r="776" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A776" s="3" t="s">
-        <v>663</v>
-      </c>
-      <c r="B776" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="B776" s="2"/>
     </row>
     <row r="777" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A777" s="3" t="s">
-        <v>664</v>
-      </c>
-      <c r="B777" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="A777" s="13" t="s">
+        <v>677</v>
+      </c>
+      <c r="B777" s="2"/>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A778" s="3" t="s">
-        <v>665</v>
+        <v>678</v>
       </c>
       <c r="B778" s="2">
-        <v>1828.125</v>
+        <v>607.75</v>
       </c>
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A779" s="3" t="s">
-        <v>666</v>
+        <v>679</v>
       </c>
       <c r="B779" s="2">
-        <v>1828.125</v>
+        <v>607.75</v>
       </c>
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A780" s="3" t="s">
-        <v>667</v>
+        <v>680</v>
       </c>
       <c r="B780" s="2">
-        <v>1828.125</v>
+        <v>607.75</v>
       </c>
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A781" s="3" t="s">
-        <v>668</v>
+        <v>681</v>
       </c>
       <c r="B781" s="2">
-        <v>1828.125</v>
+        <v>607.75</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A782" s="3" t="s">
-        <v>669</v>
+        <v>682</v>
       </c>
       <c r="B782" s="2">
-        <v>1828.125</v>
+        <v>607.75</v>
       </c>
     </row>
     <row r="783" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A783" s="3" t="s">
-        <v>670</v>
-      </c>
-      <c r="B783" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="B783" s="2"/>
     </row>
     <row r="784" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A784" s="3" t="s">
-        <v>671</v>
-      </c>
-      <c r="B784" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="A784" s="13" t="s">
+        <v>683</v>
+      </c>
+      <c r="B784" s="2"/>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" s="3" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="B785" s="2">
-        <v>1828.125</v>
+        <v>858</v>
       </c>
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="3" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="B786" s="2">
-        <v>1828.125</v>
+        <v>858</v>
       </c>
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" s="3" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="B787" s="2">
-        <v>1828.125</v>
+        <v>858</v>
       </c>
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="3" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="B788" s="2">
-        <v>1828.125</v>
+        <v>858</v>
       </c>
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="3" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="B789" s="2">
-        <v>1828.125</v>
+        <v>858</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B790" s="2"/>
+      <c r="A790" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="B790" s="2">
+        <v>858</v>
+      </c>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A791" s="1" t="s">
-        <v>677</v>
-      </c>
       <c r="B791" s="2"/>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A792" s="3" t="s">
-        <v>678</v>
-      </c>
-      <c r="B792" s="2">
-        <v>812.5</v>
-      </c>
+      <c r="B792" s="2"/>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A793" s="3" t="s">
-        <v>662</v>
-      </c>
-      <c r="B793" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="A793" s="21" t="s">
+        <v>690</v>
+      </c>
+      <c r="B793" s="2"/>
     </row>
     <row r="794" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A794" s="3" t="s">
-        <v>679</v>
-      </c>
-      <c r="B794" s="2">
-        <v>1218.75</v>
-      </c>
+      <c r="A794" s="13" t="s">
+        <v>691</v>
+      </c>
+      <c r="B794" s="2"/>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="3" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="B795" s="2">
-        <v>2096.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="3" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
       <c r="B796" s="2">
-        <v>2096.25</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" s="3" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="B797" s="2">
-        <v>3152.5</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="3" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="B798" s="2">
-        <v>1218.75</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="3" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="B799" s="2">
-        <v>1828.125</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B800" s="2"/>
+      <c r="A800" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="B800" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B801" s="2"/>
+      <c r="A801" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="B801" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A802" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="B802" s="2"/>
+      <c r="A802" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B802" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A803" s="3" t="s">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="B803" s="2">
-        <v>786.5</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A804" s="3" t="s">
-        <v>687</v>
+        <v>701</v>
       </c>
       <c r="B804" s="2">
-        <v>1085.3700000000001</v>
+        <v>812.5</v>
       </c>
     </row>
     <row r="805" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A805" s="3" t="s">
-        <v>688</v>
-      </c>
-      <c r="B805" s="2">
-        <v>1085.3700000000001</v>
-      </c>
+      <c r="B805" s="2"/>
     </row>
     <row r="806" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A806" s="13" t="s">
+        <v>369</v>
+      </c>
       <c r="B806" s="2"/>
     </row>
     <row r="807" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A807" s="1" t="s">
-        <v>689</v>
-      </c>
-      <c r="B807" s="2"/>
+      <c r="A807" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="B807" s="2">
+        <v>1137.5</v>
+      </c>
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A808" s="12" t="s">
-        <v>690</v>
-      </c>
-      <c r="B808" s="2"/>
+      <c r="A808" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="B808" s="2">
+        <v>1137.5</v>
+      </c>
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A809" s="3" t="s">
-        <v>691</v>
+        <v>704</v>
       </c>
       <c r="B809" s="2">
-        <v>446.875</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A810" s="3" t="s">
-        <v>692</v>
+        <v>705</v>
       </c>
       <c r="B810" s="2">
-        <v>446.875</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A811" s="3" t="s">
-        <v>655</v>
+        <v>466</v>
       </c>
       <c r="B811" s="2">
-        <v>446.875</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A812" s="3" t="s">
-        <v>693</v>
+        <v>706</v>
       </c>
       <c r="B812" s="2">
-        <v>446.875</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B813" s="2"/>
+      <c r="A813" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="B813" s="2">
+        <v>1137.5</v>
+      </c>
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A814" s="12" t="s">
-        <v>694</v>
-      </c>
-      <c r="B814" s="2"/>
+      <c r="A814" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="B814" s="2">
+        <v>1137.5</v>
+      </c>
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" s="3" t="s">
-        <v>695</v>
+        <v>709</v>
       </c>
       <c r="B815" s="2">
-        <v>607.75</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" s="3" t="s">
-        <v>696</v>
+        <v>710</v>
       </c>
       <c r="B816" s="2">
-        <v>607.75</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A817" s="3" t="s">
-        <v>697</v>
+        <v>711</v>
       </c>
       <c r="B817" s="2">
-        <v>607.75</v>
+        <v>1137.5</v>
       </c>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A818" s="3" t="s">
-        <v>698</v>
-      </c>
-      <c r="B818" s="2">
-        <v>607.75</v>
-      </c>
+      <c r="A818" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="B818" s="2"/>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A819" s="3" t="s">
-        <v>699</v>
+        <v>712</v>
       </c>
       <c r="B819" s="2">
-        <v>607.75</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B820" s="2"/>
+      <c r="A820" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="B820" s="2">
+        <v>1462.5</v>
+      </c>
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A821" s="12" t="s">
-        <v>700</v>
-      </c>
-      <c r="B821" s="2"/>
+      <c r="A821" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="B821" s="2">
+        <v>1462.5</v>
+      </c>
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" s="3" t="s">
-        <v>701</v>
+        <v>715</v>
       </c>
       <c r="B822" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" s="3" t="s">
-        <v>702</v>
+        <v>716</v>
       </c>
       <c r="B823" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" s="3" t="s">
-        <v>703</v>
+        <v>717</v>
       </c>
       <c r="B824" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" s="3" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="B825" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A826" s="3" t="s">
-        <v>705</v>
+        <v>719</v>
       </c>
       <c r="B826" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" s="3" t="s">
-        <v>706</v>
+        <v>720</v>
       </c>
       <c r="B827" s="2">
-        <v>858</v>
+        <v>1462.5</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B828" s="2"/>
+      <c r="A828" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="B828" s="2">
+        <v>1462.5</v>
+      </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B829" s="2"/>
+      <c r="A829" s="13" t="s">
+        <v>382</v>
+      </c>
+      <c r="B829" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A830" s="18" t="s">
-        <v>707</v>
-      </c>
-      <c r="B830" s="2"/>
+      <c r="A830" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="B830" s="2">
+        <v>1727.375</v>
+      </c>
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A831" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="B831" s="2"/>
+      <c r="A831" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="B831" s="2">
+        <v>1727.375</v>
+      </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A832" s="3" t="s">
-        <v>709</v>
+        <v>724</v>
       </c>
       <c r="B832" s="2">
-        <v>812.5</v>
+        <v>1727.375</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A833" s="3" t="s">
-        <v>710</v>
+      <c r="A833" s="13" t="s">
+        <v>572</v>
       </c>
       <c r="B833" s="2">
-        <v>812.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" s="3" t="s">
-        <v>711</v>
+        <v>725</v>
       </c>
       <c r="B834" s="2">
-        <v>812.5</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" s="3" t="s">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="B835" s="2">
-        <v>812.5</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" s="3" t="s">
-        <v>713</v>
+        <v>727</v>
       </c>
       <c r="B836" s="2">
-        <v>812.5</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" s="3" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="B837" s="2">
-        <v>812.5</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A838" s="3" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="B838" s="2">
-        <v>812.5</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A839" s="3" t="s">
-        <v>716</v>
+      <c r="A839" s="13" t="s">
+        <v>576</v>
       </c>
       <c r="B839" s="2">
-        <v>812.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" s="3" t="s">
-        <v>717</v>
+        <v>730</v>
       </c>
       <c r="B840" s="2">
-        <v>812.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" s="3" t="s">
-        <v>718</v>
+        <v>731</v>
       </c>
       <c r="B841" s="2">
-        <v>812.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B842" s="2"/>
+      <c r="A842" s="3" t="s">
+        <v>732</v>
+      </c>
+      <c r="B842" s="2">
+        <v>2133.625</v>
+      </c>
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A843" s="12" t="s">
-        <v>387</v>
-      </c>
-      <c r="B843" s="2"/>
+      <c r="A843" s="3" t="s">
+        <v>733</v>
+      </c>
+      <c r="B843" s="2">
+        <v>2133.625</v>
+      </c>
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A844" s="7" t="s">
-        <v>719</v>
+      <c r="A844" s="3" t="s">
+        <v>734</v>
       </c>
       <c r="B844" s="2">
-        <v>1137.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" s="3" t="s">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="B845" s="2">
-        <v>1137.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" s="3" t="s">
-        <v>721</v>
+        <v>736</v>
       </c>
       <c r="B846" s="2">
-        <v>1137.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A847" s="3" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="B847" s="2">
-        <v>1137.5</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A848" s="3" t="s">
-        <v>483</v>
-      </c>
       <c r="B848" s="2">
-        <v>1137.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A849" s="3" t="s">
-        <v>723</v>
+      <c r="A849" s="13" t="s">
+        <v>738</v>
       </c>
       <c r="B849" s="2">
-        <v>1137.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" s="3" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="B850" s="2">
-        <v>1137.5</v>
+        <v>1161.875</v>
       </c>
     </row>
     <row r="851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A851" s="3" t="s">
-        <v>725</v>
+        <v>701</v>
       </c>
       <c r="B851" s="2">
-        <v>1137.5</v>
+        <v>1405.625</v>
       </c>
     </row>
     <row r="852" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A852" s="3" t="s">
-        <v>726</v>
-      </c>
-      <c r="B852" s="2">
-        <v>1137.5</v>
-      </c>
+      <c r="B852" s="2"/>
     </row>
     <row r="853" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A853" s="3" t="s">
-        <v>727</v>
-      </c>
-      <c r="B853" s="2">
-        <v>1137.5</v>
-      </c>
+      <c r="A853" s="12" t="s">
+        <v>740</v>
+      </c>
+      <c r="B853" s="2"/>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A854" s="3" t="s">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="B854" s="2">
-        <v>1137.5</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A855" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="B855" s="2"/>
+      <c r="A855" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B855" s="2">
+        <v>2380.625</v>
+      </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A856" s="3" t="s">
-        <v>729</v>
+        <v>211</v>
       </c>
       <c r="B856" s="2">
-        <v>1462.5</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A857" s="3" t="s">
-        <v>730</v>
+        <v>212</v>
       </c>
       <c r="B857" s="2">
-        <v>1462.5</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A858" s="3" t="s">
-        <v>731</v>
-      </c>
-      <c r="B858" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="B858" s="2"/>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A859" s="3" t="s">
-        <v>732</v>
-      </c>
-      <c r="B859" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="A859" s="13" t="s">
+        <v>742</v>
+      </c>
+      <c r="B859" s="2"/>
     </row>
     <row r="860" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A860" s="3" t="s">
-        <v>733</v>
+        <v>743</v>
       </c>
       <c r="B860" s="2">
-        <v>1462.5</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="861" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A861" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="B861" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="B861" s="2"/>
     </row>
     <row r="862" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A862" s="3" t="s">
-        <v>735</v>
-      </c>
-      <c r="B862" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="A862" s="13" t="s">
+        <v>744</v>
+      </c>
+      <c r="B862" s="2"/>
     </row>
     <row r="863" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A863" s="3" t="s">
-        <v>736</v>
+        <v>745</v>
       </c>
       <c r="B863" s="2">
-        <v>1462.5</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="864" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A864" s="3" t="s">
-        <v>737</v>
-      </c>
-      <c r="B864" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="B864" s="2"/>
     </row>
     <row r="865" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A865" s="3" t="s">
-        <v>738</v>
-      </c>
-      <c r="B865" s="2">
-        <v>1462.5</v>
-      </c>
+      <c r="A865" s="13" t="s">
+        <v>746</v>
+      </c>
+      <c r="B865" s="2"/>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A866" s="12" t="s">
-        <v>399</v>
+      <c r="A866" s="3" t="s">
+        <v>747</v>
       </c>
       <c r="B866" s="2">
-        <v>0</v>
+        <v>1543.75</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A867" s="3" t="s">
-        <v>739</v>
+        <v>748</v>
       </c>
       <c r="B867" s="2">
-        <v>1727.375</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A868" s="3" t="s">
-        <v>740</v>
+        <v>749</v>
       </c>
       <c r="B868" s="2">
-        <v>1727.375</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A869" s="3" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="B869" s="2">
-        <v>1727.375</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A870" s="12" t="s">
-        <v>589</v>
+      <c r="A870" s="3" t="s">
+        <v>751</v>
       </c>
       <c r="B870" s="2">
-        <v>0</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A871" s="3" t="s">
-        <v>742</v>
+        <v>752</v>
       </c>
       <c r="B871" s="2">
-        <v>1930.5</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A872" s="3" t="s">
-        <v>743</v>
+        <v>753</v>
       </c>
       <c r="B872" s="2">
-        <v>1930.5</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A873" s="3" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="B873" s="2">
-        <v>1930.5</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A874" s="3" t="s">
-        <v>745</v>
-      </c>
-      <c r="B874" s="2">
-        <v>1930.5</v>
-      </c>
+      <c r="B874" s="2"/>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A875" s="3" t="s">
-        <v>746</v>
-      </c>
-      <c r="B875" s="2">
-        <v>1930.5</v>
-      </c>
+      <c r="A875" s="13" t="s">
+        <v>754</v>
+      </c>
+      <c r="B875" s="2"/>
     </row>
     <row r="876" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A876" s="12" t="s">
-        <v>593</v>
+      <c r="A876" s="3" t="s">
+        <v>755</v>
       </c>
       <c r="B876" s="2">
-        <v>0</v>
+        <v>2372.5</v>
       </c>
     </row>
     <row r="877" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A877" s="3" t="s">
-        <v>747</v>
-      </c>
-      <c r="B877" s="2">
-        <v>2133.625</v>
-      </c>
+      <c r="B877" s="2"/>
     </row>
     <row r="878" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A878" s="3" t="s">
-        <v>748</v>
-      </c>
-      <c r="B878" s="2">
-        <v>2133.625</v>
-      </c>
+      <c r="A878" s="13" t="s">
+        <v>756</v>
+      </c>
+      <c r="B878" s="2"/>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A879" s="3" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="B879" s="2">
-        <v>2133.625</v>
+        <v>2031.25</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A880" s="3" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="B880" s="2">
-        <v>2133.625</v>
-      </c>
-    </row>
-    <row r="881" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A881" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B881" s="2">
-        <v>2133.625</v>
-      </c>
-    </row>
-    <row r="882" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A882" s="3" t="s">
-        <v>752</v>
-      </c>
-      <c r="B882" s="2">
-        <v>2133.625</v>
-      </c>
-    </row>
-    <row r="883" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A883" s="3" t="s">
-        <v>753</v>
-      </c>
-      <c r="B883" s="2">
-        <v>2133.625</v>
-      </c>
-    </row>
-    <row r="884" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A884" s="3" t="s">
-        <v>754</v>
-      </c>
-      <c r="B884" s="2">
-        <v>2133.625</v>
-      </c>
-    </row>
-    <row r="885" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B885" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="886" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A886" s="12" t="s">
-        <v>755</v>
-      </c>
-      <c r="B886" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="887" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A887" s="3" t="s">
-        <v>756</v>
-      </c>
-      <c r="B887" s="2">
-        <v>1161.875</v>
-      </c>
-    </row>
-    <row r="888" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A888" s="3" t="s">
-        <v>718</v>
-      </c>
-      <c r="B888" s="2">
-        <v>1405.625</v>
-      </c>
-    </row>
-    <row r="889" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B889" s="2"/>
-    </row>
-    <row r="890" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A890" s="11" t="s">
-        <v>757</v>
-      </c>
-      <c r="B890" s="2"/>
-    </row>
-    <row r="891" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A891" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="B891" s="2">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="892" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A892" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="B892" s="2">
-        <v>2380.625</v>
-      </c>
-    </row>
-    <row r="893" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A893" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="B893" s="2">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="894" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A894" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B894" s="2">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="895" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B895" s="2"/>
-    </row>
-    <row r="896" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A896" s="12" t="s">
-        <v>759</v>
-      </c>
-      <c r="B896" s="2"/>
-    </row>
-    <row r="897" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A897" s="3" t="s">
-        <v>760</v>
-      </c>
-      <c r="B897" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="898" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B898" s="2"/>
-    </row>
-    <row r="899" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A899" s="12" t="s">
-        <v>761</v>
-      </c>
-      <c r="B899" s="2"/>
-    </row>
-    <row r="900" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A900" s="3" t="s">
-        <v>762</v>
-      </c>
-      <c r="B900" s="2">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="901" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B901" s="2"/>
-    </row>
-    <row r="902" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A902" s="12" t="s">
-        <v>763</v>
-      </c>
-      <c r="B902" s="2"/>
-    </row>
-    <row r="903" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A903" s="3" t="s">
-        <v>764</v>
-      </c>
-      <c r="B903" s="2">
-        <v>1543.75</v>
-      </c>
-    </row>
-    <row r="904" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A904" s="3" t="s">
-        <v>765</v>
-      </c>
-      <c r="B904" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="905" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A905" s="3" t="s">
-        <v>766</v>
-      </c>
-      <c r="B905" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="906" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A906" s="3" t="s">
-        <v>767</v>
-      </c>
-      <c r="B906" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="907" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A907" s="3" t="s">
-        <v>768</v>
-      </c>
-      <c r="B907" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="908" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A908" s="3" t="s">
-        <v>769</v>
-      </c>
-      <c r="B908" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="909" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A909" s="3" t="s">
-        <v>770</v>
-      </c>
-      <c r="B909" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="910" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A910" s="3" t="s">
-        <v>751</v>
-      </c>
-      <c r="B910" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="911" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B911" s="2"/>
-    </row>
-    <row r="912" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A912" s="12" t="s">
-        <v>771</v>
-      </c>
-      <c r="B912" s="2"/>
-    </row>
-    <row r="913" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A913" s="3" t="s">
-        <v>772</v>
-      </c>
-      <c r="B913" s="2">
-        <v>2372.5</v>
-      </c>
-    </row>
-    <row r="914" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B914" s="2"/>
-    </row>
-    <row r="915" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A915" s="12" t="s">
-        <v>773</v>
-      </c>
-      <c r="B915" s="2"/>
-    </row>
-    <row r="916" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A916" s="3" t="s">
-        <v>774</v>
-      </c>
-      <c r="B916" s="2">
-        <v>2031.25</v>
-      </c>
-    </row>
-    <row r="917" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A917" s="3" t="s">
-        <v>775</v>
-      </c>
-      <c r="B917" s="2">
         <v>1283.75</v>
       </c>
     </row>
-    <row r="918" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B918" s="2"/>
+    <row r="881" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B881" s="2"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>

--- a/03-product/calculadora/lista-precios-2026-07/lista-precios.xlsx
+++ b/03-product/calculadora/lista-precios-2026-07/lista-precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdmzi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8318AAB9-C350-4760-B202-A0B8CBFF8D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8722AFF-168C-44C6-B958-458419E9F1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="757">
   <si>
     <t>GUIDONI QUARTZ USD MARMOLES NATURALES</t>
   </si>
@@ -1789,16 +1789,13 @@
     <t>Navona OMG</t>
   </si>
   <si>
-    <t>( A la veta, mate poro abierto)</t>
-  </si>
-  <si>
     <t>Breccia Toscana</t>
   </si>
   <si>
     <t>Breccia Vaticano</t>
   </si>
   <si>
-    <t xml:space="preserve">Calacatta, Calacatta Arni </t>
+    <t xml:space="preserve">Calacatta Armi </t>
   </si>
   <si>
     <t>Amazonite</t>
@@ -1814,9 +1811,6 @@
   </si>
   <si>
     <t xml:space="preserve">Calacatta Extra </t>
-  </si>
-  <si>
-    <t>Statuario Exra</t>
   </si>
   <si>
     <t>Statuario Michelangelo</t>
@@ -2473,10 +2467,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2489,11 +2483,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2728,7 +2722,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G881"/>
+  <dimension ref="A1:G880"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="56.42578125" customWidth="1"/>
@@ -2751,7 +2745,7 @@
         <v>899.75600000000009</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="G2" s="5"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
@@ -2761,7 +2755,7 @@
         <v>899.75600000000009</v>
       </c>
       <c r="C3" s="4"/>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
@@ -2771,7 +2765,7 @@
         <v>899.75600000000009</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
@@ -2781,7 +2775,7 @@
         <v>736.1640000000001</v>
       </c>
       <c r="C5" s="4"/>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
@@ -2791,7 +2785,7 @@
         <v>899.75600000000009</v>
       </c>
       <c r="C6" s="4"/>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -2801,7 +2795,7 @@
         <v>777.06200000000001</v>
       </c>
       <c r="C7" s="4"/>
-      <c r="G7" s="5"/>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
@@ -2811,7 +2805,7 @@
         <v>531.67400000000009</v>
       </c>
       <c r="C8" s="4"/>
-      <c r="G8" s="5"/>
+      <c r="G8" s="6"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
@@ -2821,7 +2815,7 @@
         <v>531.67400000000009</v>
       </c>
       <c r="C9" s="4"/>
-      <c r="G9" s="5"/>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
@@ -2831,7 +2825,7 @@
         <v>531.67400000000009</v>
       </c>
       <c r="C10" s="4"/>
-      <c r="G10" s="5"/>
+      <c r="G10" s="6"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
@@ -2841,7 +2835,7 @@
         <v>633.9190000000001</v>
       </c>
       <c r="C11" s="4"/>
-      <c r="G11" s="5"/>
+      <c r="G11" s="6"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
@@ -2851,7 +2845,7 @@
         <v>654.36800000000005</v>
       </c>
       <c r="C12" s="4"/>
-      <c r="G12" s="5"/>
+      <c r="G12" s="6"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
@@ -2861,7 +2855,7 @@
         <v>736.1640000000001</v>
       </c>
       <c r="C13" s="4"/>
-      <c r="G13" s="5"/>
+      <c r="G13" s="6"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
@@ -2871,7 +2865,7 @@
         <v>736.1640000000001</v>
       </c>
       <c r="C14" s="4"/>
-      <c r="G14" s="5"/>
+      <c r="G14" s="6"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
@@ -2881,7 +2875,7 @@
         <v>654.36800000000005</v>
       </c>
       <c r="C15" s="4"/>
-      <c r="G15" s="5"/>
+      <c r="G15" s="6"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
@@ -2891,7 +2885,7 @@
         <v>1226.94</v>
       </c>
       <c r="C16" s="4"/>
-      <c r="G16" s="5"/>
+      <c r="G16" s="6"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
@@ -2901,7 +2895,7 @@
         <v>654.36800000000005</v>
       </c>
       <c r="C17" s="4"/>
-      <c r="G17" s="5"/>
+      <c r="G17" s="6"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
@@ -2911,7 +2905,7 @@
         <v>715.71500000000015</v>
       </c>
       <c r="C18" s="4"/>
-      <c r="G18" s="5"/>
+      <c r="G18" s="6"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
@@ -2921,7 +2915,7 @@
         <v>715.71500000000015</v>
       </c>
       <c r="C19" s="4"/>
-      <c r="G19" s="5"/>
+      <c r="G19" s="6"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
@@ -2931,7 +2925,7 @@
         <v>756.61300000000006</v>
       </c>
       <c r="C20" s="4"/>
-      <c r="G20" s="5"/>
+      <c r="G20" s="6"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
@@ -2941,7 +2935,7 @@
         <v>756.61300000000006</v>
       </c>
       <c r="C21" s="4"/>
-      <c r="G21" s="5"/>
+      <c r="G21" s="6"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
@@ -2951,7 +2945,7 @@
         <v>756.61300000000006</v>
       </c>
       <c r="C22" s="4"/>
-      <c r="G22" s="5"/>
+      <c r="G22" s="6"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
@@ -2961,7 +2955,7 @@
         <v>1226.94</v>
       </c>
       <c r="C23" s="4"/>
-      <c r="G23" s="5"/>
+      <c r="G23" s="6"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
@@ -2971,7 +2965,7 @@
         <v>899.75600000000009</v>
       </c>
       <c r="C24" s="4"/>
-      <c r="G24" s="5"/>
+      <c r="G24" s="6"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
@@ -2981,7 +2975,7 @@
         <v>756.61300000000006</v>
       </c>
       <c r="C25" s="4"/>
-      <c r="G25" s="5"/>
+      <c r="G25" s="6"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
@@ -2991,7 +2985,7 @@
         <v>756.61300000000006</v>
       </c>
       <c r="C26" s="4"/>
-      <c r="G26" s="5"/>
+      <c r="G26" s="6"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
@@ -3001,7 +2995,7 @@
         <v>613.47</v>
       </c>
       <c r="C27" s="4"/>
-      <c r="G27" s="5"/>
+      <c r="G27" s="6"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
@@ -3011,7 +3005,7 @@
         <v>1431.4300000000003</v>
       </c>
       <c r="C28" s="4"/>
-      <c r="G28" s="5"/>
+      <c r="G28" s="6"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="7" t="s">
@@ -3159,7 +3153,7 @@
       <c r="B47" s="2"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="14" t="s">
         <v>45</v>
       </c>
       <c r="B48" s="2"/>
@@ -3189,7 +3183,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="14" t="s">
+      <c r="A52" s="15" t="s">
         <v>49</v>
       </c>
       <c r="B52" s="2"/>
@@ -3219,7 +3213,7 @@
       <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="13" t="s">
+      <c r="A56" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B56" s="9"/>
@@ -3228,7 +3222,7 @@
       <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B57" s="9"/>
@@ -3297,7 +3291,7 @@
       <c r="B66" s="2"/>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="13" t="s">
+      <c r="A67" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B67" s="2"/>
@@ -3574,7 +3568,7 @@
       <c r="B103" s="2"/>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="13" t="s">
+      <c r="A104" s="14" t="s">
         <v>97</v>
       </c>
       <c r="B104" s="2"/>
@@ -3771,7 +3765,7 @@
       <c r="B131" s="2">
         <v>593.125</v>
       </c>
-      <c r="C131" s="6"/>
+      <c r="C131" s="5"/>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.2">
       <c r="B132" s="2"/>
@@ -4231,7 +4225,7 @@
       <c r="B194" s="2"/>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="13" t="s">
+      <c r="A195" s="14" t="s">
         <v>177</v>
       </c>
       <c r="B195" s="2">
@@ -4282,7 +4276,7 @@
       <c r="A201" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="B201" s="15">
+      <c r="B201" s="13">
         <v>660.66000000000008</v>
       </c>
     </row>
@@ -4306,7 +4300,7 @@
       <c r="A204" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B204" s="15">
+      <c r="B204" s="13">
         <v>660.66000000000008</v>
       </c>
     </row>
@@ -4378,7 +4372,7 @@
       <c r="A213" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B213" s="15">
+      <c r="B213" s="13">
         <v>660.66000000000008</v>
       </c>
     </row>
@@ -4418,7 +4412,7 @@
       <c r="A218" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B218" s="15">
+      <c r="B218" s="13">
         <v>660.66000000000008</v>
       </c>
     </row>
@@ -4426,7 +4420,7 @@
       <c r="A219" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B219" s="15">
+      <c r="B219" s="13">
         <v>660.66000000000008</v>
       </c>
     </row>
@@ -4434,7 +4428,7 @@
       <c r="A220" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="B220" s="15">
+      <c r="B220" s="13">
         <v>707.85</v>
       </c>
     </row>
@@ -4640,7 +4634,7 @@
       <c r="B248" s="2"/>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A249" s="13" t="s">
+      <c r="A249" s="14" t="s">
         <v>226</v>
       </c>
       <c r="B249" s="2"/>
@@ -4662,7 +4656,7 @@
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A252" s="13" t="s">
+      <c r="A252" s="14" t="s">
         <v>229</v>
       </c>
       <c r="B252" s="2"/>
@@ -4724,7 +4718,7 @@
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A260" s="13" t="s">
+      <c r="A260" s="14" t="s">
         <v>237</v>
       </c>
       <c r="B260" s="2"/>
@@ -4810,7 +4804,7 @@
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A271" s="13" t="s">
+      <c r="A271" s="14" t="s">
         <v>248</v>
       </c>
       <c r="B271" s="2"/>
@@ -4935,11 +4929,11 @@
       <c r="B287" s="2"/>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A288" s="13" t="s">
+      <c r="A288" s="14" t="s">
         <v>264</v>
       </c>
       <c r="B288" s="2"/>
-      <c r="G288" s="13"/>
+      <c r="G288" s="14"/>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A289" s="3" t="s">
@@ -4969,11 +4963,11 @@
       <c r="B292" s="2"/>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A293" s="13" t="s">
+      <c r="A293" s="14" t="s">
         <v>268</v>
       </c>
       <c r="B293" s="2"/>
-      <c r="G293" s="13"/>
+      <c r="G293" s="14"/>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A294" s="3" t="s">
@@ -5027,11 +5021,11 @@
       <c r="B300" s="2"/>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A301" s="13" t="s">
+      <c r="A301" s="14" t="s">
         <v>275</v>
       </c>
       <c r="B301" s="2"/>
-      <c r="G301" s="13"/>
+      <c r="G301" s="14"/>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A302" s="3" t="s">
@@ -5098,11 +5092,11 @@
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A310" s="13" t="s">
+      <c r="A310" s="14" t="s">
         <v>248</v>
       </c>
       <c r="B310" s="2"/>
-      <c r="G310" s="13"/>
+      <c r="G310" s="14"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A311" s="3" t="s">
@@ -5156,11 +5150,11 @@
       <c r="B317" s="2"/>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A318" s="13" t="s">
+      <c r="A318" s="14" t="s">
         <v>290</v>
       </c>
       <c r="B318" s="2"/>
-      <c r="G318" s="13"/>
+      <c r="G318" s="14"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A319" s="3" t="s">
@@ -5214,11 +5208,11 @@
       <c r="B325" s="2"/>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A326" s="13" t="s">
+      <c r="A326" s="14" t="s">
         <v>297</v>
       </c>
       <c r="B326" s="2"/>
-      <c r="G326" s="13"/>
+      <c r="G326" s="14"/>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A327" s="3" t="s">
@@ -5280,11 +5274,11 @@
       <c r="B334" s="2"/>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A335" s="13" t="s">
+      <c r="A335" s="14" t="s">
         <v>305</v>
       </c>
       <c r="B335" s="2"/>
-      <c r="G335" s="13"/>
+      <c r="G335" s="14"/>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B336" s="9"/>
@@ -5317,11 +5311,11 @@
       <c r="B340" s="2"/>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A341" s="13" t="s">
+      <c r="A341" s="14" t="s">
         <v>309</v>
       </c>
       <c r="B341" s="2"/>
-      <c r="G341" s="13"/>
+      <c r="G341" s="14"/>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A342" s="3" t="s">
@@ -5362,7 +5356,7 @@
       <c r="B347" s="2"/>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A348" s="13" t="s">
+      <c r="A348" s="14" t="s">
         <v>264</v>
       </c>
       <c r="B348" s="2"/>
@@ -5443,7 +5437,7 @@
       <c r="B358" s="2"/>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A359" s="13" t="s">
+      <c r="A359" s="14" t="s">
         <v>268</v>
       </c>
       <c r="B359" s="2"/>
@@ -5548,7 +5542,7 @@
       <c r="B372" s="2"/>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A373" s="13" t="s">
+      <c r="A373" s="14" t="s">
         <v>237</v>
       </c>
       <c r="B373" s="2"/>
@@ -5661,7 +5655,7 @@
       <c r="B387" s="2"/>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A388" s="13" t="s">
+      <c r="A388" s="14" t="s">
         <v>248</v>
       </c>
       <c r="B388" s="2"/>
@@ -5710,7 +5704,7 @@
       <c r="B394" s="2"/>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A395" s="13" t="s">
+      <c r="A395" s="14" t="s">
         <v>290</v>
       </c>
       <c r="B395" s="2"/>
@@ -5757,11 +5751,11 @@
       <c r="B401" s="2"/>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A402" s="13"/>
+      <c r="A402" s="14"/>
       <c r="B402" s="2"/>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A403" s="13" t="s">
+      <c r="A403" s="14" t="s">
         <v>264</v>
       </c>
       <c r="B403" s="2"/>
@@ -5858,7 +5852,7 @@
       <c r="B415" s="2"/>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A416" s="13" t="s">
+      <c r="A416" s="14" t="s">
         <v>369</v>
       </c>
       <c r="B416" s="2"/>
@@ -5923,7 +5917,7 @@
       <c r="B424" s="2"/>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A425" s="13" t="s">
+      <c r="A425" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B425" s="2"/>
@@ -5972,7 +5966,7 @@
       <c r="B431" s="2"/>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A432" s="13" t="s">
+      <c r="A432" s="14" t="s">
         <v>382</v>
       </c>
       <c r="B432" s="2"/>
@@ -6027,7 +6021,7 @@
       <c r="B439" s="2"/>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A440" s="13" t="s">
+      <c r="A440" s="14" t="s">
         <v>226</v>
       </c>
       <c r="B440" s="2"/>
@@ -6129,7 +6123,7 @@
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A453" s="13" t="s">
+      <c r="A453" s="14" t="s">
         <v>229</v>
       </c>
       <c r="B453" s="2"/>
@@ -6213,7 +6207,7 @@
       <c r="B464" s="2"/>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A465" s="13" t="s">
+      <c r="A465" s="14" t="s">
         <v>275</v>
       </c>
       <c r="B465" s="2"/>
@@ -6290,7 +6284,7 @@
       <c r="B475" s="2"/>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A476" s="13" t="s">
+      <c r="A476" s="14" t="s">
         <v>248</v>
       </c>
       <c r="B476" s="2"/>
@@ -6352,7 +6346,7 @@
       </c>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A484" s="13" t="s">
+      <c r="A484" s="14" t="s">
         <v>290</v>
       </c>
       <c r="B484" s="2"/>
@@ -6423,7 +6417,7 @@
       </c>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A493" s="13" t="s">
+      <c r="A493" s="14" t="s">
         <v>297</v>
       </c>
       <c r="B493" s="2"/>
@@ -7537,7 +7531,7 @@
       <c r="B634" s="2"/>
     </row>
     <row r="635" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A635" s="13" t="s">
+      <c r="A635" s="14" t="s">
         <v>369</v>
       </c>
       <c r="B635" s="2"/>
@@ -7551,23 +7545,20 @@
       </c>
     </row>
     <row r="637" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A637" s="3" t="s">
-        <v>565</v>
-      </c>
       <c r="B637" s="2"/>
     </row>
     <row r="638" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B638" s="2"/>
     </row>
     <row r="639" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A639" s="13" t="s">
+      <c r="A639" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B639" s="2"/>
     </row>
     <row r="640" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A640" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B640" s="2">
         <v>2905.5</v>
@@ -7575,7 +7566,7 @@
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A641" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B641" s="2">
         <v>2905.5</v>
@@ -7583,7 +7574,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A642" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B642" s="2">
         <v>2905.5</v>
@@ -7598,14 +7589,14 @@
       </c>
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A644" s="13" t="s">
+      <c r="A644" s="14" t="s">
         <v>382</v>
       </c>
       <c r="B644" s="2"/>
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A645" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B645" s="2">
         <v>3250</v>
@@ -7613,7 +7604,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A646" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B646" s="2">
         <v>3250</v>
@@ -7621,7 +7612,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A647" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B647" s="2">
         <v>3250</v>
@@ -7631,14 +7622,14 @@
       <c r="B648" s="2"/>
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A649" s="13" t="s">
-        <v>572</v>
+      <c r="A649" s="14" t="s">
+        <v>571</v>
       </c>
       <c r="B649" s="2"/>
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A650" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B650" s="2">
         <v>3859.375</v>
@@ -7646,32 +7637,32 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A651" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B651" s="2">
         <v>3859.375</v>
       </c>
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A652" s="3" t="s">
+      <c r="B652" s="2"/>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A653" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="B653" s="2"/>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A654" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B652" s="2">
-        <v>3859.375</v>
-      </c>
-    </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B653" s="2"/>
-    </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A654" s="13" t="s">
-        <v>576</v>
-      </c>
-      <c r="B654" s="2"/>
+      <c r="B654" s="2">
+        <v>4671.875</v>
+      </c>
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A655" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B655" s="2">
         <v>4671.875</v>
@@ -7679,7 +7670,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A656" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B656" s="2">
         <v>4671.875</v>
@@ -7687,63 +7678,63 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A657" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B657" s="2">
         <v>4671.875</v>
       </c>
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A658" s="3" t="s">
+      <c r="B658" s="2"/>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A659" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="B659" s="2"/>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A660" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="B658" s="2">
-        <v>4671.875</v>
-      </c>
-    </row>
-    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B659" s="2"/>
-    </row>
-    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A660" s="13" t="s">
-        <v>581</v>
-      </c>
-      <c r="B660" s="2"/>
+      <c r="B660" s="2">
+        <v>7312.5</v>
+      </c>
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A661" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B661" s="2">
         <v>7312.5</v>
       </c>
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A662" s="3" t="s">
+      <c r="B662" s="2"/>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A663" s="1" t="s">
+        <v>582</v>
+      </c>
+      <c r="B663" s="2"/>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A664" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B664" s="2"/>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A665" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="B662" s="2">
-        <v>7312.5</v>
-      </c>
-    </row>
-    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B663" s="2"/>
-    </row>
-    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A664" s="1" t="s">
-        <v>584</v>
-      </c>
-      <c r="B664" s="2"/>
-    </row>
-    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A665" s="13" t="s">
-        <v>226</v>
-      </c>
-      <c r="B665" s="2"/>
+      <c r="B665" s="2">
+        <v>406.25</v>
+      </c>
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A666" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B666" s="2">
         <v>406.25</v>
@@ -7751,7 +7742,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A667" s="3" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B667" s="2">
         <v>406.25</v>
@@ -7759,7 +7750,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A668" s="3" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B668" s="2">
         <v>406.25</v>
@@ -7767,7 +7758,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A669" s="3" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B669" s="2">
         <v>406.25</v>
@@ -7775,7 +7766,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A670" s="3" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B670" s="2">
         <v>406.25</v>
@@ -7783,7 +7774,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A671" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B671" s="2">
         <v>406.25</v>
@@ -7791,32 +7782,32 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A672" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B672" s="2">
         <v>406.25</v>
       </c>
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A673" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="B673" s="2">
-        <v>406.25</v>
-      </c>
+      <c r="B673" s="2"/>
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A674" s="14" t="s">
+        <v>268</v>
+      </c>
       <c r="B674" s="2"/>
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A675" s="13" t="s">
-        <v>268</v>
-      </c>
-      <c r="B675" s="2"/>
+      <c r="A675" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B675" s="2">
+        <v>549.25</v>
+      </c>
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A676" s="3" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B676" s="2">
         <v>549.25</v>
@@ -7824,7 +7815,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A677" s="3" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B677" s="2">
         <v>549.25</v>
@@ -7832,7 +7823,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A678" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B678" s="2">
         <v>549.25</v>
@@ -7840,7 +7831,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A679" s="3" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B679" s="2">
         <v>549.25</v>
@@ -7848,7 +7839,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A680" s="3" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="B680" s="2">
         <v>549.25</v>
@@ -7856,7 +7847,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A681" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B681" s="2">
         <v>549.25</v>
@@ -7864,7 +7855,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A682" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B682" s="2">
         <v>549.25</v>
@@ -7872,7 +7863,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A683" s="3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B683" s="2">
         <v>549.25</v>
@@ -7880,32 +7871,32 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A684" s="3" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B684" s="2">
         <v>549.25</v>
       </c>
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A685" s="3" t="s">
+      <c r="B685" s="2"/>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A686" s="14" t="s">
+        <v>601</v>
+      </c>
+      <c r="B686" s="2"/>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A687" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="B685" s="2">
-        <v>549.25</v>
-      </c>
-    </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B686" s="2"/>
-    </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A687" s="13" t="s">
-        <v>603</v>
-      </c>
-      <c r="B687" s="2"/>
+      <c r="B687" s="2">
+        <v>690.625</v>
+      </c>
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A688" s="3" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B688" s="2">
         <v>690.625</v>
@@ -7913,7 +7904,7 @@
     </row>
     <row r="689" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A689" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B689" s="2">
         <v>690.625</v>
@@ -7921,7 +7912,7 @@
     </row>
     <row r="690" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A690" s="3" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B690" s="2">
         <v>690.625</v>
@@ -7929,7 +7920,7 @@
     </row>
     <row r="691" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A691" s="3" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B691" s="2">
         <v>690.625</v>
@@ -7937,7 +7928,7 @@
     </row>
     <row r="692" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A692" s="3" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B692" s="2">
         <v>690.625</v>
@@ -7945,7 +7936,7 @@
     </row>
     <row r="693" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A693" s="3" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B693" s="2">
         <v>690.625</v>
@@ -7953,7 +7944,7 @@
     </row>
     <row r="694" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A694" s="3" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B694" s="2">
         <v>690.625</v>
@@ -7961,7 +7952,7 @@
     </row>
     <row r="695" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A695" s="3" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B695" s="2">
         <v>690.625</v>
@@ -7969,7 +7960,7 @@
     </row>
     <row r="696" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A696" s="3" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B696" s="2">
         <v>690.625</v>
@@ -7977,7 +7968,7 @@
     </row>
     <row r="697" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A697" s="3" t="s">
-        <v>613</v>
+        <v>172</v>
       </c>
       <c r="B697" s="2">
         <v>690.625</v>
@@ -7985,7 +7976,7 @@
     </row>
     <row r="698" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A698" s="3" t="s">
-        <v>172</v>
+        <v>612</v>
       </c>
       <c r="B698" s="2">
         <v>690.625</v>
@@ -7993,7 +7984,7 @@
     </row>
     <row r="699" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A699" s="3" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B699" s="2">
         <v>690.625</v>
@@ -8001,7 +7992,7 @@
     </row>
     <row r="700" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A700" s="3" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B700" s="2">
         <v>690.625</v>
@@ -8009,7 +8000,7 @@
     </row>
     <row r="701" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A701" s="3" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B701" s="2">
         <v>690.625</v>
@@ -8017,7 +8008,7 @@
     </row>
     <row r="702" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A702" s="3" t="s">
-        <v>617</v>
+        <v>507</v>
       </c>
       <c r="B702" s="2">
         <v>690.625</v>
@@ -8025,32 +8016,32 @@
     </row>
     <row r="703" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A703" s="3" t="s">
-        <v>507</v>
+        <v>616</v>
       </c>
       <c r="B703" s="2">
         <v>690.625</v>
       </c>
     </row>
     <row r="704" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A704" s="3" t="s">
-        <v>618</v>
-      </c>
-      <c r="B704" s="2">
-        <v>690.625</v>
-      </c>
+      <c r="B704" s="2"/>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A705" s="14" t="s">
+        <v>382</v>
+      </c>
       <c r="B705" s="2"/>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A706" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="B706" s="2"/>
+      <c r="A706" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="B706" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A707" s="3" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B707" s="2">
         <v>812.5</v>
@@ -8058,7 +8049,7 @@
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A708" s="3" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B708" s="2">
         <v>812.5</v>
@@ -8066,7 +8057,7 @@
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A709" s="3" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B709" s="2">
         <v>812.5</v>
@@ -8074,7 +8065,7 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A710" s="3" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B710" s="2">
         <v>812.5</v>
@@ -8082,7 +8073,7 @@
     </row>
     <row r="711" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A711" s="3" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B711" s="2">
         <v>812.5</v>
@@ -8090,7 +8081,7 @@
     </row>
     <row r="712" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A712" s="3" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B712" s="2">
         <v>812.5</v>
@@ -8098,7 +8089,7 @@
     </row>
     <row r="713" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A713" s="3" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B713" s="2">
         <v>812.5</v>
@@ -8106,7 +8097,7 @@
     </row>
     <row r="714" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A714" s="3" t="s">
-        <v>626</v>
+        <v>168</v>
       </c>
       <c r="B714" s="2">
         <v>812.5</v>
@@ -8114,7 +8105,7 @@
     </row>
     <row r="715" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A715" s="3" t="s">
-        <v>168</v>
+        <v>625</v>
       </c>
       <c r="B715" s="2">
         <v>812.5</v>
@@ -8122,7 +8113,7 @@
     </row>
     <row r="716" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A716" s="3" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B716" s="2">
         <v>812.5</v>
@@ -8130,32 +8121,32 @@
     </row>
     <row r="717" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A717" s="3" t="s">
-        <v>628</v>
+        <v>164</v>
       </c>
       <c r="B717" s="2">
         <v>812.5</v>
       </c>
     </row>
     <row r="718" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A718" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B718" s="2">
-        <v>812.5</v>
-      </c>
+      <c r="B718" s="2"/>
     </row>
     <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A719" s="14" t="s">
+        <v>627</v>
+      </c>
       <c r="B719" s="2"/>
     </row>
     <row r="720" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A720" s="13" t="s">
-        <v>629</v>
-      </c>
-      <c r="B720" s="2"/>
+      <c r="A720" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B720" s="2">
+        <v>1218.75</v>
+      </c>
     </row>
     <row r="721" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A721" s="3" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B721" s="2">
         <v>1218.75</v>
@@ -8163,7 +8154,7 @@
     </row>
     <row r="722" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A722" s="3" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B722" s="2">
         <v>1218.75</v>
@@ -8171,7 +8162,7 @@
     </row>
     <row r="723" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A723" s="3" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B723" s="2">
         <v>1218.75</v>
@@ -8179,7 +8170,7 @@
     </row>
     <row r="724" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A724" s="3" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B724" s="2">
         <v>1218.75</v>
@@ -8187,7 +8178,7 @@
     </row>
     <row r="725" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A725" s="3" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B725" s="2">
         <v>1218.75</v>
@@ -8195,7 +8186,7 @@
     </row>
     <row r="726" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A726" s="3" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B726" s="2">
         <v>1218.75</v>
@@ -8203,7 +8194,7 @@
     </row>
     <row r="727" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A727" s="3" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B727" s="2">
         <v>1218.75</v>
@@ -8211,7 +8202,7 @@
     </row>
     <row r="728" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A728" s="3" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B728" s="2">
         <v>1218.75</v>
@@ -8219,7 +8210,7 @@
     </row>
     <row r="729" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A729" s="3" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B729" s="2">
         <v>1218.75</v>
@@ -8227,7 +8218,7 @@
     </row>
     <row r="730" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A730" s="3" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B730" s="2">
         <v>1218.75</v>
@@ -8235,7 +8226,7 @@
     </row>
     <row r="731" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A731" s="3" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B731" s="2">
         <v>1218.75</v>
@@ -8243,7 +8234,7 @@
     </row>
     <row r="732" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A732" s="3" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B732" s="2">
         <v>1218.75</v>
@@ -8251,7 +8242,7 @@
     </row>
     <row r="733" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A733" s="3" t="s">
-        <v>642</v>
+        <v>159</v>
       </c>
       <c r="B733" s="2">
         <v>1218.75</v>
@@ -8259,32 +8250,32 @@
     </row>
     <row r="734" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A734" s="3" t="s">
-        <v>159</v>
+        <v>641</v>
       </c>
       <c r="B734" s="2">
         <v>1218.75</v>
       </c>
     </row>
     <row r="735" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A735" s="3" t="s">
+      <c r="B735" s="2"/>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A736" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="B736" s="2"/>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A737" s="3" t="s">
         <v>643</v>
       </c>
-      <c r="B735" s="2">
-        <v>1218.75</v>
-      </c>
-    </row>
-    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B736" s="2"/>
-    </row>
-    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A737" s="13" t="s">
-        <v>644</v>
-      </c>
-      <c r="B737" s="2"/>
+      <c r="B737" s="2">
+        <v>1828.125</v>
+      </c>
     </row>
     <row r="738" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A738" s="3" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B738" s="2">
         <v>1828.125</v>
@@ -8292,7 +8283,7 @@
     </row>
     <row r="739" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A739" s="3" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B739" s="2">
         <v>1828.125</v>
@@ -8300,7 +8291,7 @@
     </row>
     <row r="740" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A740" s="3" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B740" s="2">
         <v>1828.125</v>
@@ -8308,7 +8299,7 @@
     </row>
     <row r="741" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A741" s="3" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B741" s="2">
         <v>1828.125</v>
@@ -8316,7 +8307,7 @@
     </row>
     <row r="742" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A742" s="3" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="B742" s="2">
         <v>1828.125</v>
@@ -8324,7 +8315,7 @@
     </row>
     <row r="743" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A743" s="3" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B743" s="2">
         <v>1828.125</v>
@@ -8332,7 +8323,7 @@
     </row>
     <row r="744" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A744" s="3" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B744" s="2">
         <v>1828.125</v>
@@ -8340,7 +8331,7 @@
     </row>
     <row r="745" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A745" s="3" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B745" s="2">
         <v>1828.125</v>
@@ -8348,7 +8339,7 @@
     </row>
     <row r="746" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A746" s="3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B746" s="2">
         <v>1828.125</v>
@@ -8356,7 +8347,7 @@
     </row>
     <row r="747" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A747" s="3" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B747" s="2">
         <v>1828.125</v>
@@ -8364,7 +8355,7 @@
     </row>
     <row r="748" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A748" s="3" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B748" s="2">
         <v>1828.125</v>
@@ -8372,7 +8363,7 @@
     </row>
     <row r="749" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A749" s="3" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B749" s="2">
         <v>1828.125</v>
@@ -8380,7 +8371,7 @@
     </row>
     <row r="750" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A750" s="3" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B750" s="2">
         <v>1828.125</v>
@@ -8388,56 +8379,56 @@
     </row>
     <row r="751" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A751" s="3" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B751" s="2">
         <v>1828.125</v>
       </c>
     </row>
     <row r="752" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A752" s="3" t="s">
+      <c r="B752" s="2"/>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A753" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="B753" s="2"/>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A754" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B752" s="2">
-        <v>1828.125</v>
-      </c>
-    </row>
-    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B753" s="2"/>
-    </row>
-    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A754" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="B754" s="2"/>
+      <c r="B754" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="755" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A755" s="3" t="s">
-        <v>661</v>
+        <v>643</v>
       </c>
       <c r="B755" s="2">
-        <v>812.5</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="756" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A756" s="3" t="s">
-        <v>645</v>
+        <v>660</v>
       </c>
       <c r="B756" s="2">
-        <v>1828.125</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="757" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A757" s="3" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B757" s="2">
-        <v>1218.75</v>
+        <v>2096.25</v>
       </c>
     </row>
     <row r="758" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A758" s="3" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B758" s="2">
         <v>2096.25</v>
@@ -8445,90 +8436,90 @@
     </row>
     <row r="759" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A759" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B759" s="2">
-        <v>2096.25</v>
+        <v>3152.5</v>
       </c>
     </row>
     <row r="760" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A760" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B760" s="2">
-        <v>3152.5</v>
+        <v>1218.75</v>
       </c>
     </row>
     <row r="761" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A761" s="3" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="B761" s="2">
-        <v>1218.75</v>
+        <v>1828.125</v>
       </c>
     </row>
     <row r="762" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A762" s="3" t="s">
-        <v>667</v>
-      </c>
-      <c r="B762" s="2">
-        <v>1828.125</v>
-      </c>
+      <c r="B762" s="2"/>
     </row>
     <row r="763" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B763" s="2"/>
     </row>
     <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A764" s="19" t="s">
+        <v>666</v>
+      </c>
       <c r="B764" s="2"/>
     </row>
     <row r="765" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A765" s="19" t="s">
-        <v>668</v>
-      </c>
-      <c r="B765" s="2"/>
+      <c r="A765" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="B765" s="2">
+        <v>786.5</v>
+      </c>
     </row>
     <row r="766" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A766" s="3" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B766" s="2">
-        <v>786.5</v>
+        <v>1085.3700000000001</v>
       </c>
     </row>
     <row r="767" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A767" s="3" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B767" s="2">
         <v>1085.3700000000001</v>
       </c>
     </row>
     <row r="768" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A768" s="3" t="s">
+      <c r="B768" s="2"/>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A769" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="B769" s="2"/>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A770" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="B768" s="2">
-        <v>1085.3700000000001</v>
-      </c>
-    </row>
-    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B769" s="2"/>
-    </row>
-    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A770" s="1" t="s">
+      <c r="B770" s="2"/>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A771" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="B770" s="2"/>
-    </row>
-    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A771" s="13" t="s">
-        <v>673</v>
-      </c>
-      <c r="B771" s="2"/>
+      <c r="B771" s="2">
+        <v>446.875</v>
+      </c>
     </row>
     <row r="772" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A772" s="3" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B772" s="2">
         <v>446.875</v>
@@ -8536,7 +8527,7 @@
     </row>
     <row r="773" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A773" s="3" t="s">
-        <v>675</v>
+        <v>636</v>
       </c>
       <c r="B773" s="2">
         <v>446.875</v>
@@ -8544,32 +8535,32 @@
     </row>
     <row r="774" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A774" s="3" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
       <c r="B774" s="2">
         <v>446.875</v>
       </c>
     </row>
     <row r="775" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A775" s="3" t="s">
+      <c r="B775" s="2"/>
+    </row>
+    <row r="776" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A776" s="14" t="s">
+        <v>675</v>
+      </c>
+      <c r="B776" s="2"/>
+    </row>
+    <row r="777" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A777" s="3" t="s">
         <v>676</v>
       </c>
-      <c r="B775" s="2">
-        <v>446.875</v>
-      </c>
-    </row>
-    <row r="776" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B776" s="2"/>
-    </row>
-    <row r="777" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A777" s="13" t="s">
-        <v>677</v>
-      </c>
-      <c r="B777" s="2"/>
+      <c r="B777" s="2">
+        <v>607.75</v>
+      </c>
     </row>
     <row r="778" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A778" s="3" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B778" s="2">
         <v>607.75</v>
@@ -8577,7 +8568,7 @@
     </row>
     <row r="779" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A779" s="3" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B779" s="2">
         <v>607.75</v>
@@ -8585,7 +8576,7 @@
     </row>
     <row r="780" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A780" s="3" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B780" s="2">
         <v>607.75</v>
@@ -8593,32 +8584,32 @@
     </row>
     <row r="781" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A781" s="3" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B781" s="2">
         <v>607.75</v>
       </c>
     </row>
     <row r="782" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A782" s="3" t="s">
+      <c r="B782" s="2"/>
+    </row>
+    <row r="783" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A783" s="14" t="s">
+        <v>681</v>
+      </c>
+      <c r="B783" s="2"/>
+    </row>
+    <row r="784" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A784" s="3" t="s">
         <v>682</v>
       </c>
-      <c r="B782" s="2">
-        <v>607.75</v>
-      </c>
-    </row>
-    <row r="783" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B783" s="2"/>
-    </row>
-    <row r="784" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A784" s="13" t="s">
-        <v>683</v>
-      </c>
-      <c r="B784" s="2"/>
+      <c r="B784" s="2">
+        <v>858</v>
+      </c>
     </row>
     <row r="785" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A785" s="3" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B785" s="2">
         <v>858</v>
@@ -8626,7 +8617,7 @@
     </row>
     <row r="786" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A786" s="3" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B786" s="2">
         <v>858</v>
@@ -8634,7 +8625,7 @@
     </row>
     <row r="787" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A787" s="3" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B787" s="2">
         <v>858</v>
@@ -8642,7 +8633,7 @@
     </row>
     <row r="788" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A788" s="3" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B788" s="2">
         <v>858</v>
@@ -8650,41 +8641,41 @@
     </row>
     <row r="789" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A789" s="3" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B789" s="2">
         <v>858</v>
       </c>
     </row>
     <row r="790" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A790" s="3" t="s">
-        <v>689</v>
-      </c>
-      <c r="B790" s="2">
-        <v>858</v>
-      </c>
+      <c r="B790" s="2"/>
     </row>
     <row r="791" spans="1:2" x14ac:dyDescent="0.2">
       <c r="B791" s="2"/>
     </row>
     <row r="792" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A792" s="21" t="s">
+        <v>688</v>
+      </c>
       <c r="B792" s="2"/>
     </row>
     <row r="793" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A793" s="21" t="s">
+      <c r="A793" s="14" t="s">
+        <v>689</v>
+      </c>
+      <c r="B793" s="2"/>
+    </row>
+    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A794" s="3" t="s">
         <v>690</v>
       </c>
-      <c r="B793" s="2"/>
-    </row>
-    <row r="794" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A794" s="13" t="s">
-        <v>691</v>
-      </c>
-      <c r="B794" s="2"/>
+      <c r="B794" s="2">
+        <v>812.5</v>
+      </c>
     </row>
     <row r="795" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A795" s="3" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B795" s="2">
         <v>812.5</v>
@@ -8692,7 +8683,7 @@
     </row>
     <row r="796" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A796" s="3" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B796" s="2">
         <v>812.5</v>
@@ -8700,7 +8691,7 @@
     </row>
     <row r="797" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A797" s="3" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B797" s="2">
         <v>812.5</v>
@@ -8708,7 +8699,7 @@
     </row>
     <row r="798" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A798" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B798" s="2">
         <v>812.5</v>
@@ -8716,7 +8707,7 @@
     </row>
     <row r="799" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A799" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B799" s="2">
         <v>812.5</v>
@@ -8724,7 +8715,7 @@
     </row>
     <row r="800" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A800" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B800" s="2">
         <v>812.5</v>
@@ -8732,7 +8723,7 @@
     </row>
     <row r="801" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A801" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B801" s="2">
         <v>812.5</v>
@@ -8740,7 +8731,7 @@
     </row>
     <row r="802" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A802" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B802" s="2">
         <v>812.5</v>
@@ -8748,32 +8739,32 @@
     </row>
     <row r="803" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A803" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B803" s="2">
         <v>812.5</v>
       </c>
     </row>
     <row r="804" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A804" s="3" t="s">
+      <c r="B804" s="2"/>
+    </row>
+    <row r="805" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A805" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="B805" s="2"/>
+    </row>
+    <row r="806" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A806" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B806" s="2">
+        <v>1137.5</v>
+      </c>
+    </row>
+    <row r="807" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A807" s="3" t="s">
         <v>701</v>
-      </c>
-      <c r="B804" s="2">
-        <v>812.5</v>
-      </c>
-    </row>
-    <row r="805" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B805" s="2"/>
-    </row>
-    <row r="806" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A806" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="B806" s="2"/>
-    </row>
-    <row r="807" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A807" s="8" t="s">
-        <v>702</v>
       </c>
       <c r="B807" s="2">
         <v>1137.5</v>
@@ -8781,7 +8772,7 @@
     </row>
     <row r="808" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A808" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B808" s="2">
         <v>1137.5</v>
@@ -8789,7 +8780,7 @@
     </row>
     <row r="809" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A809" s="3" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B809" s="2">
         <v>1137.5</v>
@@ -8797,7 +8788,7 @@
     </row>
     <row r="810" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A810" s="3" t="s">
-        <v>705</v>
+        <v>466</v>
       </c>
       <c r="B810" s="2">
         <v>1137.5</v>
@@ -8805,7 +8796,7 @@
     </row>
     <row r="811" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A811" s="3" t="s">
-        <v>466</v>
+        <v>704</v>
       </c>
       <c r="B811" s="2">
         <v>1137.5</v>
@@ -8813,7 +8804,7 @@
     </row>
     <row r="812" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A812" s="3" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B812" s="2">
         <v>1137.5</v>
@@ -8821,7 +8812,7 @@
     </row>
     <row r="813" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A813" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B813" s="2">
         <v>1137.5</v>
@@ -8829,7 +8820,7 @@
     </row>
     <row r="814" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A814" s="3" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B814" s="2">
         <v>1137.5</v>
@@ -8837,7 +8828,7 @@
     </row>
     <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" s="3" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B815" s="2">
         <v>1137.5</v>
@@ -8845,29 +8836,29 @@
     </row>
     <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" s="3" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B816" s="2">
         <v>1137.5</v>
       </c>
     </row>
     <row r="817" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A817" s="3" t="s">
-        <v>711</v>
-      </c>
-      <c r="B817" s="2">
-        <v>1137.5</v>
-      </c>
+      <c r="A817" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="B817" s="2"/>
     </row>
     <row r="818" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A818" s="13" t="s">
-        <v>275</v>
-      </c>
-      <c r="B818" s="2"/>
+      <c r="A818" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B818" s="2">
+        <v>1462.5</v>
+      </c>
     </row>
     <row r="819" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A819" s="3" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B819" s="2">
         <v>1462.5</v>
@@ -8875,7 +8866,7 @@
     </row>
     <row r="820" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A820" s="3" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B820" s="2">
         <v>1462.5</v>
@@ -8883,7 +8874,7 @@
     </row>
     <row r="821" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A821" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B821" s="2">
         <v>1462.5</v>
@@ -8891,7 +8882,7 @@
     </row>
     <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" s="3" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B822" s="2">
         <v>1462.5</v>
@@ -8899,7 +8890,7 @@
     </row>
     <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" s="3" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B823" s="2">
         <v>1462.5</v>
@@ -8907,7 +8898,7 @@
     </row>
     <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" s="3" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B824" s="2">
         <v>1462.5</v>
@@ -8915,7 +8906,7 @@
     </row>
     <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" s="3" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B825" s="2">
         <v>1462.5</v>
@@ -8923,7 +8914,7 @@
     </row>
     <row r="826" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A826" s="3" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B826" s="2">
         <v>1462.5</v>
@@ -8931,31 +8922,31 @@
     </row>
     <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" s="3" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B827" s="2">
         <v>1462.5</v>
       </c>
     </row>
     <row r="828" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A828" s="3" t="s">
-        <v>721</v>
+      <c r="A828" s="14" t="s">
+        <v>382</v>
       </c>
       <c r="B828" s="2">
-        <v>1462.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A829" s="13" t="s">
-        <v>382</v>
+      <c r="A829" s="3" t="s">
+        <v>720</v>
       </c>
       <c r="B829" s="2">
-        <v>0</v>
+        <v>1727.375</v>
       </c>
     </row>
     <row r="830" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A830" s="3" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B830" s="2">
         <v>1727.375</v>
@@ -8963,31 +8954,31 @@
     </row>
     <row r="831" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A831" s="3" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B831" s="2">
         <v>1727.375</v>
       </c>
     </row>
     <row r="832" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A832" s="3" t="s">
-        <v>724</v>
+      <c r="A832" s="14" t="s">
+        <v>571</v>
       </c>
       <c r="B832" s="2">
-        <v>1727.375</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A833" s="13" t="s">
-        <v>572</v>
+      <c r="A833" s="3" t="s">
+        <v>723</v>
       </c>
       <c r="B833" s="2">
-        <v>0</v>
+        <v>1930.5</v>
       </c>
     </row>
     <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" s="3" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B834" s="2">
         <v>1930.5</v>
@@ -8995,7 +8986,7 @@
     </row>
     <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" s="3" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B835" s="2">
         <v>1930.5</v>
@@ -9003,7 +8994,7 @@
     </row>
     <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B836" s="2">
         <v>1930.5</v>
@@ -9011,31 +9002,31 @@
     </row>
     <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B837" s="2">
         <v>1930.5</v>
       </c>
     </row>
     <row r="838" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A838" s="3" t="s">
-        <v>729</v>
+      <c r="A838" s="14" t="s">
+        <v>574</v>
       </c>
       <c r="B838" s="2">
-        <v>1930.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A839" s="13" t="s">
-        <v>576</v>
+      <c r="A839" s="3" t="s">
+        <v>728</v>
       </c>
       <c r="B839" s="2">
-        <v>0</v>
+        <v>2133.625</v>
       </c>
     </row>
     <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" s="3" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B840" s="2">
         <v>2133.625</v>
@@ -9043,7 +9034,7 @@
     </row>
     <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" s="3" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B841" s="2">
         <v>2133.625</v>
@@ -9051,7 +9042,7 @@
     </row>
     <row r="842" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A842" s="3" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B842" s="2">
         <v>2133.625</v>
@@ -9059,7 +9050,7 @@
     </row>
     <row r="843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A843" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B843" s="2">
         <v>2133.625</v>
@@ -9067,7 +9058,7 @@
     </row>
     <row r="844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A844" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B844" s="2">
         <v>2133.625</v>
@@ -9075,7 +9066,7 @@
     </row>
     <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" s="3" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B845" s="2">
         <v>2133.625</v>
@@ -9083,144 +9074,144 @@
     </row>
     <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" s="3" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B846" s="2">
         <v>2133.625</v>
       </c>
     </row>
     <row r="847" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A847" s="3" t="s">
-        <v>737</v>
-      </c>
       <c r="B847" s="2">
-        <v>2133.625</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A848" s="14" t="s">
+        <v>736</v>
+      </c>
       <c r="B848" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="849" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A849" s="13" t="s">
-        <v>738</v>
+      <c r="A849" s="3" t="s">
+        <v>737</v>
       </c>
       <c r="B849" s="2">
-        <v>0</v>
+        <v>1161.875</v>
       </c>
     </row>
     <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="B850" s="2">
+        <v>1405.625</v>
+      </c>
+    </row>
+    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B851" s="2"/>
+    </row>
+    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A852" s="12" t="s">
+        <v>738</v>
+      </c>
+      <c r="B852" s="2"/>
+    </row>
+    <row r="853" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A853" s="3" t="s">
         <v>739</v>
       </c>
-      <c r="B850" s="2">
-        <v>1161.875</v>
-      </c>
-    </row>
-    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A851" s="3" t="s">
-        <v>701</v>
-      </c>
-      <c r="B851" s="2">
-        <v>1405.625</v>
-      </c>
-    </row>
-    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B852" s="2"/>
-    </row>
-    <row r="853" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A853" s="12" t="s">
-        <v>740</v>
-      </c>
-      <c r="B853" s="2"/>
+      <c r="B853" s="2">
+        <v>1625</v>
+      </c>
     </row>
     <row r="854" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A854" s="3" t="s">
-        <v>741</v>
+        <v>199</v>
       </c>
       <c r="B854" s="2">
-        <v>1625</v>
+        <v>2380.625</v>
       </c>
     </row>
     <row r="855" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A855" s="3" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="B855" s="2">
-        <v>2380.625</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="856" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A856" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B856" s="2">
         <v>1625</v>
       </c>
     </row>
     <row r="857" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A857" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B857" s="2">
-        <v>1625</v>
-      </c>
+      <c r="B857" s="2"/>
     </row>
     <row r="858" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A858" s="14" t="s">
+        <v>740</v>
+      </c>
       <c r="B858" s="2"/>
     </row>
     <row r="859" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A859" s="13" t="s">
+      <c r="A859" s="3" t="s">
+        <v>741</v>
+      </c>
+      <c r="B859" s="2">
+        <v>2136.875</v>
+      </c>
+    </row>
+    <row r="860" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B860" s="2"/>
+    </row>
+    <row r="861" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A861" s="14" t="s">
         <v>742</v>
       </c>
-      <c r="B859" s="2"/>
-    </row>
-    <row r="860" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A860" s="3" t="s">
+      <c r="B861" s="2"/>
+    </row>
+    <row r="862" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A862" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="B860" s="2">
-        <v>2136.875</v>
-      </c>
-    </row>
-    <row r="861" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B861" s="2"/>
-    </row>
-    <row r="862" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A862" s="13" t="s">
+      <c r="B862" s="2">
+        <v>3250</v>
+      </c>
+    </row>
+    <row r="863" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B863" s="2"/>
+    </row>
+    <row r="864" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A864" s="14" t="s">
         <v>744</v>
       </c>
-      <c r="B862" s="2"/>
-    </row>
-    <row r="863" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A863" s="3" t="s">
+      <c r="B864" s="2"/>
+    </row>
+    <row r="865" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A865" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B863" s="2">
-        <v>3250</v>
-      </c>
-    </row>
-    <row r="864" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B864" s="2"/>
-    </row>
-    <row r="865" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A865" s="13" t="s">
-        <v>746</v>
-      </c>
-      <c r="B865" s="2"/>
+      <c r="B865" s="2">
+        <v>1543.75</v>
+      </c>
     </row>
     <row r="866" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A866" s="3" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B866" s="2">
-        <v>1543.75</v>
+        <v>2136.875</v>
       </c>
     </row>
     <row r="867" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A867" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B867" s="2">
         <v>2136.875</v>
@@ -9228,7 +9219,7 @@
     </row>
     <row r="868" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A868" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B868" s="2">
         <v>2136.875</v>
@@ -9236,7 +9227,7 @@
     </row>
     <row r="869" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A869" s="3" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B869" s="2">
         <v>2136.875</v>
@@ -9244,7 +9235,7 @@
     </row>
     <row r="870" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A870" s="3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B870" s="2">
         <v>2136.875</v>
@@ -9252,7 +9243,7 @@
     </row>
     <row r="871" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A871" s="3" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B871" s="2">
         <v>2136.875</v>
@@ -9260,64 +9251,56 @@
     </row>
     <row r="872" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A872" s="3" t="s">
-        <v>753</v>
+        <v>732</v>
       </c>
       <c r="B872" s="2">
         <v>2136.875</v>
       </c>
     </row>
     <row r="873" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A873" s="3" t="s">
-        <v>734</v>
-      </c>
-      <c r="B873" s="2">
-        <v>2136.875</v>
-      </c>
+      <c r="B873" s="2"/>
     </row>
     <row r="874" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A874" s="14" t="s">
+        <v>752</v>
+      </c>
       <c r="B874" s="2"/>
     </row>
     <row r="875" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A875" s="13" t="s">
+      <c r="A875" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="B875" s="2">
+        <v>2372.5</v>
+      </c>
+    </row>
+    <row r="876" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="B876" s="2"/>
+    </row>
+    <row r="877" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A877" s="14" t="s">
         <v>754</v>
       </c>
-      <c r="B875" s="2"/>
-    </row>
-    <row r="876" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A876" s="3" t="s">
+      <c r="B877" s="2"/>
+    </row>
+    <row r="878" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A878" s="3" t="s">
         <v>755</v>
       </c>
-      <c r="B876" s="2">
-        <v>2372.5</v>
-      </c>
-    </row>
-    <row r="877" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="B877" s="2"/>
-    </row>
-    <row r="878" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A878" s="13" t="s">
-        <v>756</v>
-      </c>
-      <c r="B878" s="2"/>
+      <c r="B878" s="2">
+        <v>2031.25</v>
+      </c>
     </row>
     <row r="879" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A879" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B879" s="2">
-        <v>2031.25</v>
+        <v>1283.75</v>
       </c>
     </row>
     <row r="880" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A880" s="3" t="s">
-        <v>758</v>
-      </c>
-      <c r="B880" s="2">
-        <v>1283.75</v>
-      </c>
-    </row>
-    <row r="881" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B881" s="2"/>
+      <c r="B880" s="2"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1" gridLines="1"/>
